--- a/artfynd/A 52871-2025 artfynd.xlsx
+++ b/artfynd/A 52871-2025 artfynd.xlsx
@@ -4482,7 +4482,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129338899</v>
+        <v>129338511</v>
       </c>
       <c r="B33" t="n">
         <v>98727</v>
@@ -4512,12 +4512,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>dm²</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -4531,10 +4526,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>525712</v>
+        <v>525680</v>
       </c>
       <c r="R33" t="n">
-        <v>6716201</v>
+        <v>6716143</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4566,7 +4561,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4576,7 +4571,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:31</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ca 20 bladrosetter 1 överblommade</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4603,7 +4603,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129338511</v>
+        <v>129338899</v>
       </c>
       <c r="B34" t="n">
         <v>98727</v>
@@ -4633,7 +4633,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -4647,10 +4652,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>525680</v>
+        <v>525712</v>
       </c>
       <c r="R34" t="n">
-        <v>6716143</v>
+        <v>6716201</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4682,7 +4687,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4692,12 +4697,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:31</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ca 20 bladrosetter 1 överblommade</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD34" t="b">

--- a/artfynd/A 52871-2025 artfynd.xlsx
+++ b/artfynd/A 52871-2025 artfynd.xlsx
@@ -4482,7 +4482,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129338511</v>
+        <v>129338899</v>
       </c>
       <c r="B33" t="n">
         <v>98727</v>
@@ -4512,7 +4512,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -4526,10 +4531,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>525680</v>
+        <v>525712</v>
       </c>
       <c r="R33" t="n">
-        <v>6716143</v>
+        <v>6716201</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4561,7 +4566,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4571,12 +4576,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:31</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ca 20 bladrosetter 1 överblommade</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4603,7 +4603,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129338899</v>
+        <v>129338511</v>
       </c>
       <c r="B34" t="n">
         <v>98727</v>
@@ -4633,12 +4633,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>dm²</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -4652,10 +4647,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>525712</v>
+        <v>525680</v>
       </c>
       <c r="R34" t="n">
-        <v>6716201</v>
+        <v>6716143</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4687,7 +4682,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4697,7 +4692,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:31</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ca 20 bladrosetter 1 överblommade</t>
         </is>
       </c>
       <c r="AD34" t="b">

--- a/artfynd/A 52871-2025 artfynd.xlsx
+++ b/artfynd/A 52871-2025 artfynd.xlsx
@@ -3773,7 +3773,7 @@
         <v>129339939</v>
       </c>
       <c r="B27" t="n">
-        <v>92873</v>
+        <v>92901</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3889,7 +3889,7 @@
         <v>129340627</v>
       </c>
       <c r="B28" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4122,7 +4122,7 @@
         <v>129338657</v>
       </c>
       <c r="B30" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4248,7 +4248,7 @@
         <v>129339191</v>
       </c>
       <c r="B31" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4364,7 +4364,7 @@
         <v>129339551</v>
       </c>
       <c r="B32" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4482,10 +4482,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129338511</v>
+        <v>129338899</v>
       </c>
       <c r="B33" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4512,7 +4512,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -4526,10 +4531,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>525680</v>
+        <v>525712</v>
       </c>
       <c r="R33" t="n">
-        <v>6716143</v>
+        <v>6716201</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4561,7 +4566,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4571,12 +4576,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:31</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ca 20 bladrosetter 1 överblommade</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4603,10 +4603,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129338899</v>
+        <v>129338511</v>
       </c>
       <c r="B34" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4633,12 +4633,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>dm²</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -4652,10 +4647,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>525712</v>
+        <v>525680</v>
       </c>
       <c r="R34" t="n">
-        <v>6716201</v>
+        <v>6716143</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4687,7 +4682,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4697,7 +4692,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:31</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ca 20 bladrosetter 1 överblommade</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4727,7 +4727,7 @@
         <v>129339499</v>
       </c>
       <c r="B35" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4853,7 +4853,7 @@
         <v>129340696</v>
       </c>
       <c r="B36" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4974,7 +4974,7 @@
         <v>129338834</v>
       </c>
       <c r="B37" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5090,7 +5090,7 @@
         <v>129338590</v>
       </c>
       <c r="B38" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 52871-2025 artfynd.xlsx
+++ b/artfynd/A 52871-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY38"/>
+  <dimension ref="A1:AY40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3773,7 +3773,7 @@
         <v>129339939</v>
       </c>
       <c r="B27" t="n">
-        <v>92901</v>
+        <v>92907</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3889,7 +3889,7 @@
         <v>129340627</v>
       </c>
       <c r="B28" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4122,7 +4122,7 @@
         <v>129338657</v>
       </c>
       <c r="B30" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4248,7 +4248,7 @@
         <v>129339191</v>
       </c>
       <c r="B31" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4364,7 +4364,7 @@
         <v>129339551</v>
       </c>
       <c r="B32" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4482,10 +4482,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129338899</v>
+        <v>129338511</v>
       </c>
       <c r="B33" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4512,12 +4512,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>dm²</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -4531,10 +4526,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>525712</v>
+        <v>525680</v>
       </c>
       <c r="R33" t="n">
-        <v>6716201</v>
+        <v>6716143</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4566,7 +4561,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4576,7 +4571,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:31</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ca 20 bladrosetter 1 överblommade</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4603,10 +4603,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129338511</v>
+        <v>129338899</v>
       </c>
       <c r="B34" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4633,7 +4633,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -4647,10 +4652,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>525680</v>
+        <v>525712</v>
       </c>
       <c r="R34" t="n">
-        <v>6716143</v>
+        <v>6716201</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4682,7 +4687,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4692,12 +4697,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:31</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ca 20 bladrosetter 1 överblommade</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4727,7 +4727,7 @@
         <v>129339499</v>
       </c>
       <c r="B35" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4853,7 +4853,7 @@
         <v>129340696</v>
       </c>
       <c r="B36" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4974,7 +4974,7 @@
         <v>129338834</v>
       </c>
       <c r="B37" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5090,7 +5090,7 @@
         <v>129338590</v>
       </c>
       <c r="B38" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5200,6 +5200,235 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>129727312</v>
+      </c>
+      <c r="B39" t="n">
+        <v>58592</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>208250</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Åkergroda</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Rana arvalis</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Nilsson, 1842</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Åkergroda, Dlr</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>525655</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6716145</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Aspeboda</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Fotad och eftergranskad av grodexpert</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Milada Alexandersson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Milada Alexandersson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>129747025</v>
+      </c>
+      <c r="B40" t="n">
+        <v>57576</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>102621</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Sparvuggla</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Glaucidium passerinum</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Stående död tall, Dlr</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>525786</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6716281</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Aspeboda</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Sitter på toppen av en gran och bevakar.</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Milada Alexandersson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Milada Alexandersson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 52871-2025 artfynd.xlsx
+++ b/artfynd/A 52871-2025 artfynd.xlsx
@@ -3773,7 +3773,7 @@
         <v>129339939</v>
       </c>
       <c r="B27" t="n">
-        <v>92907</v>
+        <v>92908</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3889,7 +3889,7 @@
         <v>129340627</v>
       </c>
       <c r="B28" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4122,7 +4122,7 @@
         <v>129338657</v>
       </c>
       <c r="B30" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4248,7 +4248,7 @@
         <v>129339191</v>
       </c>
       <c r="B31" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4364,7 +4364,7 @@
         <v>129339551</v>
       </c>
       <c r="B32" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4482,10 +4482,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129338511</v>
+        <v>129338899</v>
       </c>
       <c r="B33" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4512,7 +4512,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -4526,10 +4531,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>525680</v>
+        <v>525712</v>
       </c>
       <c r="R33" t="n">
-        <v>6716143</v>
+        <v>6716201</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4561,7 +4566,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4571,12 +4576,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:31</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ca 20 bladrosetter 1 överblommade</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4603,10 +4603,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129338899</v>
+        <v>129338511</v>
       </c>
       <c r="B34" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4633,12 +4633,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>dm²</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -4652,10 +4647,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>525712</v>
+        <v>525680</v>
       </c>
       <c r="R34" t="n">
-        <v>6716201</v>
+        <v>6716143</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4687,7 +4682,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4697,7 +4692,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:31</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ca 20 bladrosetter 1 överblommade</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4727,7 +4727,7 @@
         <v>129339499</v>
       </c>
       <c r="B35" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4853,7 +4853,7 @@
         <v>129340696</v>
       </c>
       <c r="B36" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4974,7 +4974,7 @@
         <v>129338834</v>
       </c>
       <c r="B37" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5090,7 +5090,7 @@
         <v>129338590</v>
       </c>
       <c r="B38" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5206,7 +5206,7 @@
         <v>129727312</v>
       </c>
       <c r="B39" t="n">
-        <v>58592</v>
+        <v>58593</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5318,7 +5318,7 @@
         <v>129747025</v>
       </c>
       <c r="B40" t="n">
-        <v>57576</v>
+        <v>57577</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 52871-2025 artfynd.xlsx
+++ b/artfynd/A 52871-2025 artfynd.xlsx
@@ -3773,7 +3773,7 @@
         <v>129339939</v>
       </c>
       <c r="B27" t="n">
-        <v>92908</v>
+        <v>92913</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3889,7 +3889,7 @@
         <v>129340627</v>
       </c>
       <c r="B28" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4122,7 +4122,7 @@
         <v>129338657</v>
       </c>
       <c r="B30" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4248,7 +4248,7 @@
         <v>129339191</v>
       </c>
       <c r="B31" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4364,7 +4364,7 @@
         <v>129339551</v>
       </c>
       <c r="B32" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4482,10 +4482,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129338899</v>
+        <v>129338511</v>
       </c>
       <c r="B33" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4512,12 +4512,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>dm²</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -4531,10 +4526,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>525712</v>
+        <v>525680</v>
       </c>
       <c r="R33" t="n">
-        <v>6716201</v>
+        <v>6716143</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4566,7 +4561,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4576,7 +4571,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:31</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ca 20 bladrosetter 1 överblommade</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4603,10 +4603,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129338511</v>
+        <v>129338899</v>
       </c>
       <c r="B34" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4633,7 +4633,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -4647,10 +4652,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>525680</v>
+        <v>525712</v>
       </c>
       <c r="R34" t="n">
-        <v>6716143</v>
+        <v>6716201</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4682,7 +4687,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4692,12 +4697,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:31</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ca 20 bladrosetter 1 överblommade</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4727,7 +4727,7 @@
         <v>129339499</v>
       </c>
       <c r="B35" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4853,7 +4853,7 @@
         <v>129340696</v>
       </c>
       <c r="B36" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4974,7 +4974,7 @@
         <v>129338834</v>
       </c>
       <c r="B37" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5090,7 +5090,7 @@
         <v>129338590</v>
       </c>
       <c r="B38" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 52871-2025 artfynd.xlsx
+++ b/artfynd/A 52871-2025 artfynd.xlsx
@@ -4482,7 +4482,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129338511</v>
+        <v>129338899</v>
       </c>
       <c r="B33" t="n">
         <v>98774</v>
@@ -4512,7 +4512,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -4526,10 +4531,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>525680</v>
+        <v>525712</v>
       </c>
       <c r="R33" t="n">
-        <v>6716143</v>
+        <v>6716201</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4561,7 +4566,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4571,12 +4576,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:31</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ca 20 bladrosetter 1 överblommade</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4603,7 +4603,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129338899</v>
+        <v>129338511</v>
       </c>
       <c r="B34" t="n">
         <v>98774</v>
@@ -4633,12 +4633,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>dm²</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -4652,10 +4647,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>525712</v>
+        <v>525680</v>
       </c>
       <c r="R34" t="n">
-        <v>6716201</v>
+        <v>6716143</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4687,7 +4682,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4697,7 +4692,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:31</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ca 20 bladrosetter 1 överblommade</t>
         </is>
       </c>
       <c r="AD34" t="b">

--- a/artfynd/A 52871-2025 artfynd.xlsx
+++ b/artfynd/A 52871-2025 artfynd.xlsx
@@ -4482,7 +4482,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129338899</v>
+        <v>129338511</v>
       </c>
       <c r="B33" t="n">
         <v>98774</v>
@@ -4512,12 +4512,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>dm²</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -4531,10 +4526,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>525712</v>
+        <v>525680</v>
       </c>
       <c r="R33" t="n">
-        <v>6716201</v>
+        <v>6716143</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4566,7 +4561,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4576,7 +4571,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:31</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ca 20 bladrosetter 1 överblommade</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4603,7 +4603,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129338511</v>
+        <v>129338899</v>
       </c>
       <c r="B34" t="n">
         <v>98774</v>
@@ -4633,7 +4633,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -4647,10 +4652,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>525680</v>
+        <v>525712</v>
       </c>
       <c r="R34" t="n">
-        <v>6716143</v>
+        <v>6716201</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4682,7 +4687,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4692,12 +4697,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:31</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ca 20 bladrosetter 1 överblommade</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD34" t="b">

--- a/artfynd/A 52871-2025 artfynd.xlsx
+++ b/artfynd/A 52871-2025 artfynd.xlsx
@@ -5318,7 +5318,7 @@
         <v>129747025</v>
       </c>
       <c r="B40" t="n">
-        <v>57577</v>
+        <v>57578</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 52871-2025 artfynd.xlsx
+++ b/artfynd/A 52871-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY40"/>
+  <dimension ref="A1:AY43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5206,7 +5206,7 @@
         <v>129727312</v>
       </c>
       <c r="B39" t="n">
-        <v>58593</v>
+        <v>58596</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5430,6 +5430,332 @@
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>129979175</v>
+      </c>
+      <c r="B41" t="n">
+        <v>57893</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Stående död tall, Dlr</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>525766</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6716251</v>
+      </c>
+      <c r="S41" t="n">
+        <v>5</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Aspeboda</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Milada Alexandersson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Milada Alexandersson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>129979188</v>
+      </c>
+      <c r="B42" t="n">
+        <v>57734</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Stående död tall, "smedjor", Stående död tall, "smedjor", Dlr</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>525724</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6716195</v>
+      </c>
+      <c r="S42" t="n">
+        <v>5</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Aspeboda</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Milada Alexandersson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Milada Alexandersson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>129979221</v>
+      </c>
+      <c r="B43" t="n">
+        <v>57729</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>100110</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Gråspett</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Picus canus</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>J.F. Gmelin, 1788</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Stående död tall, Stående död tall, Dlr</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>525782</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6716244</v>
+      </c>
+      <c r="S43" t="n">
+        <v>5</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Aspeboda</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Milada Alexandersson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Milada Alexandersson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 52871-2025 artfynd.xlsx
+++ b/artfynd/A 52871-2025 artfynd.xlsx
@@ -5206,7 +5206,7 @@
         <v>129727312</v>
       </c>
       <c r="B39" t="n">
-        <v>58596</v>
+        <v>58599</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5318,7 +5318,7 @@
         <v>129747025</v>
       </c>
       <c r="B40" t="n">
-        <v>57578</v>
+        <v>57581</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5435,7 +5435,7 @@
         <v>129979175</v>
       </c>
       <c r="B41" t="n">
-        <v>57893</v>
+        <v>57896</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5537,7 +5537,7 @@
         <v>129979188</v>
       </c>
       <c r="B42" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5649,7 +5649,7 @@
         <v>129979221</v>
       </c>
       <c r="B43" t="n">
-        <v>57729</v>
+        <v>57732</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 52871-2025 artfynd.xlsx
+++ b/artfynd/A 52871-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY43"/>
+  <dimension ref="A1:AY45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5756,6 +5756,223 @@
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>130016904</v>
+      </c>
+      <c r="B44" t="n">
+        <v>98797</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Hundviken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>525602</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6716070</v>
+      </c>
+      <c r="S44" t="n">
+        <v>5</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Aspeboda</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Milada Alexandersson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Milada Alexandersson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>130022082</v>
+      </c>
+      <c r="B45" t="n">
+        <v>56672</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>208255</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Skogsödla</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Zootoca vivipara</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Jacquin, 1787)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Intill väg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>525632</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6716152</v>
+      </c>
+      <c r="S45" t="n">
+        <v>5</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Aspeboda</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF45" t="inlineStr"/>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AY45" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 52871-2025 artfynd.xlsx
+++ b/artfynd/A 52871-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY45"/>
+  <dimension ref="A1:AY48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5973,6 +5973,350 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AY45" t="inlineStr"/>
     </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>129731617</v>
+      </c>
+      <c r="B46" t="n">
+        <v>57598</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>100137</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Slaguggla</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Strix uralensis</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Pallas, 1771</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>rastande</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Stråtenbo 62, Stråtenbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>525535</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6716136</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Aspeboda</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Vuxen slaguggla på besök från närliggande boplats</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Kenneth Smith</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Kenneth Smith</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr">
+        <is>
+          <t>Privat inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>130044230</v>
+      </c>
+      <c r="B47" t="n">
+        <v>58601</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>208249</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Vanlig groda</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Rana temporaria</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Intill väg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>525653</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6716143</v>
+      </c>
+      <c r="S47" t="n">
+        <v>5</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Aspeboda</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-08-09</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-08-09</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Stor för att vara vanlig groda. Närmast paddstorlek.</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF47" t="inlineStr"/>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Daniel Alexandersson</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Daniel Alexandersson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>130044041</v>
+      </c>
+      <c r="B48" t="n">
+        <v>97668</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Hundviken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>525776</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6716252</v>
+      </c>
+      <c r="S48" t="n">
+        <v>25</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Aspeboda</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF48" t="inlineStr"/>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Daniel Alexandersson</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Daniel Alexandersson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 52871-2025 artfynd.xlsx
+++ b/artfynd/A 52871-2025 artfynd.xlsx
@@ -5758,32 +5758,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130016904</v>
+        <v>130022082</v>
       </c>
       <c r="B44" t="n">
-        <v>98797</v>
+        <v>56672</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>208255</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Zootoca vivipara</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Jacquin, 1787)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -5793,19 +5793,23 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Hundviken, Dlr</t>
+          <t>Intill väg, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>525602</v>
+        <v>525632</v>
       </c>
       <c r="R44" t="n">
-        <v>6716070</v>
+        <v>6716152</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5832,22 +5836,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-12-07</t>
-        </is>
-      </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>13:58</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-12-07</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>13:58</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5856,50 +5850,51 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Milada Alexandersson</t>
+          <t>Daniel Alexandersson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Milada Alexandersson</t>
+          <t>Daniel Alexandersson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130022082</v>
+        <v>130016904</v>
       </c>
       <c r="B45" t="n">
-        <v>56672</v>
+        <v>98798</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>208255</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Zootoca vivipara</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Jacquin, 1787)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -5909,23 +5904,19 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Intill väg, Dlr</t>
+          <t>Hundviken, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>525632</v>
+        <v>525602</v>
       </c>
       <c r="R45" t="n">
-        <v>6716152</v>
+        <v>6716070</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5952,12 +5943,22 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5966,11 +5967,20 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Milada Alexandersson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Milada Alexandersson</t>
+        </is>
+      </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
@@ -6220,7 +6230,7 @@
         <v>130044041</v>
       </c>
       <c r="B48" t="n">
-        <v>97668</v>
+        <v>97669</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 52871-2025 artfynd.xlsx
+++ b/artfynd/A 52871-2025 artfynd.xlsx
@@ -5206,7 +5206,7 @@
         <v>129727312</v>
       </c>
       <c r="B39" t="n">
-        <v>58599</v>
+        <v>58600</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5435,7 +5435,7 @@
         <v>129979175</v>
       </c>
       <c r="B41" t="n">
-        <v>57896</v>
+        <v>57897</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5872,7 +5872,7 @@
         <v>130016904</v>
       </c>
       <c r="B45" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6114,7 +6114,7 @@
         <v>130044230</v>
       </c>
       <c r="B47" t="n">
-        <v>58601</v>
+        <v>58602</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6230,7 +6230,7 @@
         <v>130044041</v>
       </c>
       <c r="B48" t="n">
-        <v>97669</v>
+        <v>97686</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 52871-2025 artfynd.xlsx
+++ b/artfynd/A 52871-2025 artfynd.xlsx
@@ -5872,7 +5872,7 @@
         <v>130016904</v>
       </c>
       <c r="B45" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6456,7 +6456,7 @@
         <v>130044041</v>
       </c>
       <c r="B50" t="n">
-        <v>97708</v>
+        <v>97710</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/A 52871-2025 artfynd.xlsx
+++ b/artfynd/A 52871-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY50"/>
+  <dimension ref="A1:AY32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127315588</v>
+        <v>127351108</v>
       </c>
       <c r="B2" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -705,22 +705,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -729,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>525666</v>
+        <v>525674</v>
       </c>
       <c r="R2" t="n">
-        <v>6716159</v>
+        <v>6716190</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -759,22 +749,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-08-09</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>18:56</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-08-09</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>18:56</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>1 stjälke</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -801,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127315514</v>
+        <v>127351427</v>
       </c>
       <c r="B3" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -831,22 +826,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -855,10 +840,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>525676</v>
+        <v>525690</v>
       </c>
       <c r="R3" t="n">
-        <v>6716168</v>
+        <v>6716183</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -885,22 +870,27 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-08-09</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-08-09</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>1 stjälke</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -927,10 +917,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127316295</v>
+        <v>127351240</v>
       </c>
       <c r="B4" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -957,7 +947,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -965,29 +955,19 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Hundviken, Hundviken, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>525743</v>
+        <v>525680</v>
       </c>
       <c r="R4" t="n">
-        <v>6716220</v>
+        <v>6716185</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1011,22 +991,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-08-09</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-08-09</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1053,10 +1033,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127314167</v>
+        <v>127351678</v>
       </c>
       <c r="B5" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1083,17 +1063,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1102,13 +1077,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>525686</v>
+        <v>525682</v>
       </c>
       <c r="R5" t="n">
-        <v>6716155</v>
+        <v>6716183</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1132,22 +1107,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-08-09</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>19:23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-08-09</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>19:23</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1174,10 +1149,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127315222</v>
+        <v>127351377</v>
       </c>
       <c r="B6" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1204,22 +1179,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1228,10 +1193,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>525682</v>
+        <v>525680</v>
       </c>
       <c r="R6" t="n">
-        <v>6716184</v>
+        <v>6716172</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1258,22 +1223,27 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-08-09</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>19:07</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-08-09</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>19:07</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>1 stjälke</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1300,10 +1270,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127315716</v>
+        <v>127351465</v>
       </c>
       <c r="B7" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1330,22 +1300,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1354,10 +1314,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>525670</v>
+        <v>525676</v>
       </c>
       <c r="R7" t="n">
-        <v>6716189</v>
+        <v>6716177</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1384,22 +1344,27 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-08-09</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>19:13</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-08-09</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>19:13</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>2 stjälkar</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1426,10 +1391,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127316344</v>
+        <v>127350965</v>
       </c>
       <c r="B8" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1456,17 +1421,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1475,13 +1435,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>525736</v>
+        <v>525685</v>
       </c>
       <c r="R8" t="n">
-        <v>6716217</v>
+        <v>6716229</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1505,22 +1465,27 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-08-09</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>18:49</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-08-09</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>18:49</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>1 stjälke</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1547,32 +1512,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127316136</v>
+        <v>129339939</v>
       </c>
       <c r="B9" t="n">
-        <v>98469</v>
+        <v>92913</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>5966</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1580,34 +1545,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hundviken, Hundviken, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>525712</v>
+        <v>525799</v>
       </c>
       <c r="R9" t="n">
-        <v>6716193</v>
+        <v>6716284</v>
       </c>
       <c r="S9" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1631,22 +1581,27 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Med tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1673,10 +1628,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127316228</v>
+        <v>129340627</v>
       </c>
       <c r="B10" t="n">
-        <v>98469</v>
+        <v>98774</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1703,22 +1658,17 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1727,13 +1677,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>525740</v>
+        <v>525709</v>
       </c>
       <c r="R10" t="n">
-        <v>6716244</v>
+        <v>6716198</v>
       </c>
       <c r="S10" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1757,22 +1707,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1799,52 +1749,38 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127314992</v>
+        <v>129339605</v>
       </c>
       <c r="B11" t="n">
-        <v>98469</v>
+        <v>8450</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1853,13 +1789,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>525694</v>
+        <v>525780</v>
       </c>
       <c r="R11" t="n">
-        <v>6716178</v>
+        <v>6716226</v>
       </c>
       <c r="S11" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1883,22 +1819,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1925,10 +1861,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127316105</v>
+        <v>129338657</v>
       </c>
       <c r="B12" t="n">
-        <v>98469</v>
+        <v>98774</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1955,22 +1891,17 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1979,13 +1910,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>525712</v>
+        <v>525677</v>
       </c>
       <c r="R12" t="n">
-        <v>6716192</v>
+        <v>6716163</v>
       </c>
       <c r="S12" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2009,22 +1940,27 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>10:38</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>1 överblommad</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2051,10 +1987,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127316409</v>
+        <v>129339191</v>
       </c>
       <c r="B13" t="n">
-        <v>98469</v>
+        <v>98774</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2081,22 +2017,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2105,13 +2031,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>525735</v>
+        <v>525746</v>
       </c>
       <c r="R13" t="n">
-        <v>6716213</v>
+        <v>6716215</v>
       </c>
       <c r="S13" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2135,22 +2061,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2177,10 +2103,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127315619</v>
+        <v>129339551</v>
       </c>
       <c r="B14" t="n">
-        <v>98469</v>
+        <v>98774</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2207,22 +2133,17 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2231,13 +2152,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>525656</v>
+        <v>525769</v>
       </c>
       <c r="R14" t="n">
-        <v>6716166</v>
+        <v>6716224</v>
       </c>
       <c r="S14" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2261,22 +2182,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2303,10 +2224,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127315460</v>
+        <v>129338511</v>
       </c>
       <c r="B15" t="n">
-        <v>98469</v>
+        <v>98774</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2333,22 +2254,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2357,13 +2268,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>525688</v>
+        <v>525680</v>
       </c>
       <c r="R15" t="n">
-        <v>6716179</v>
+        <v>6716143</v>
       </c>
       <c r="S15" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2387,22 +2298,27 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:31</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ca 20 bladrosetter 1 överblommade</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2429,10 +2345,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127315125</v>
+        <v>129338899</v>
       </c>
       <c r="B16" t="n">
-        <v>98469</v>
+        <v>98774</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2459,22 +2375,17 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2483,13 +2394,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>525684</v>
+        <v>525712</v>
       </c>
       <c r="R16" t="n">
-        <v>6716162</v>
+        <v>6716201</v>
       </c>
       <c r="S16" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2513,22 +2424,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2555,10 +2466,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127316162</v>
+        <v>129339499</v>
       </c>
       <c r="B17" t="n">
-        <v>98469</v>
+        <v>98774</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2585,22 +2496,17 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2609,13 +2515,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>525752</v>
+        <v>525771</v>
       </c>
       <c r="R17" t="n">
-        <v>6716206</v>
+        <v>6716245</v>
       </c>
       <c r="S17" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2639,22 +2545,27 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>11:09</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Spridda över ca 0,5 m2</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2681,10 +2592,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127313556</v>
+        <v>129340696</v>
       </c>
       <c r="B18" t="n">
-        <v>98469</v>
+        <v>98774</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2711,7 +2622,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2719,29 +2630,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Hundviken, Hundviken, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>525685</v>
+        <v>525672</v>
       </c>
       <c r="R18" t="n">
-        <v>6716175</v>
+        <v>6716190</v>
       </c>
       <c r="S18" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2765,22 +2666,27 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:59</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På stenblock! 2 överblommade</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2807,10 +2713,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127314541</v>
+        <v>129338834</v>
       </c>
       <c r="B19" t="n">
-        <v>98469</v>
+        <v>98774</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2837,22 +2743,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2861,13 +2757,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>525690</v>
+        <v>525715</v>
       </c>
       <c r="R19" t="n">
-        <v>6716175</v>
+        <v>6716181</v>
       </c>
       <c r="S19" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2891,22 +2787,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2933,10 +2829,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127351108</v>
+        <v>129338590</v>
       </c>
       <c r="B20" t="n">
-        <v>98470</v>
+        <v>98774</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2963,12 +2859,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2977,10 +2873,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>525674</v>
+        <v>525673</v>
       </c>
       <c r="R20" t="n">
-        <v>6716190</v>
+        <v>6716152</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -3007,27 +2903,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-08-09</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>18:56</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-08-09</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>18:56</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>1 stjälke</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3054,57 +2945,57 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127351427</v>
+        <v>129727312</v>
       </c>
       <c r="B21" t="n">
-        <v>98470</v>
+        <v>58600</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>208250</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Hundviken, Hundviken, Dlr</t>
+          <t>Åkergroda, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>525690</v>
+        <v>525655</v>
       </c>
       <c r="R21" t="n">
-        <v>6716183</v>
+        <v>6716145</v>
       </c>
       <c r="S21" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3128,27 +3019,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-08-09</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>19:10</t>
+          <t>2025-08-17</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-08-09</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>19:10</t>
+          <t>2025-08-17</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>1 stjälke</t>
+          <t>Fotad och eftergranskad av grodexpert</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3157,6 +3038,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3175,57 +3057,53 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127351240</v>
+        <v>129747025</v>
       </c>
       <c r="B22" t="n">
-        <v>98470</v>
+        <v>57581</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>102621</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Hundviken, Hundviken, Dlr</t>
+          <t>Stående död tall, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>525680</v>
+        <v>525786</v>
       </c>
       <c r="R22" t="n">
-        <v>6716185</v>
+        <v>6716281</v>
       </c>
       <c r="S22" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3249,22 +3127,27 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-08-09</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-08-09</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Sitter på toppen av en gran och bevakar.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3291,54 +3174,50 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127351678</v>
+        <v>129979175</v>
       </c>
       <c r="B23" t="n">
-        <v>98470</v>
+        <v>57983</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>103020</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Hundviken, Hundviken, Dlr</t>
+          <t>Stående död tall, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>525682</v>
+        <v>525766</v>
       </c>
       <c r="R23" t="n">
-        <v>6716183</v>
+        <v>6716251</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3365,22 +3244,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-08-09</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>19:23</t>
+          <t>2025-04-11</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-08-09</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>19:23</t>
+          <t>2025-04-11</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3407,57 +3276,53 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127351377</v>
+        <v>129979188</v>
       </c>
       <c r="B24" t="n">
-        <v>98470</v>
+        <v>57823</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Hundviken, Hundviken, Dlr</t>
+          <t>Stående död tall, "smedjor", Stående död tall, "smedjor", Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>525680</v>
+        <v>525724</v>
       </c>
       <c r="R24" t="n">
-        <v>6716172</v>
+        <v>6716195</v>
       </c>
       <c r="S24" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3481,27 +3346,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-08-09</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>19:07</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-08-09</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>19:07</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>1 stjälke</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3528,57 +3388,53 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127351465</v>
+        <v>129979221</v>
       </c>
       <c r="B25" t="n">
-        <v>98470</v>
+        <v>57818</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>100110</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>J.F. Gmelin, 1788</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Hundviken, Hundviken, Dlr</t>
+          <t>Stående död tall, Stående död tall, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>525676</v>
+        <v>525782</v>
       </c>
       <c r="R25" t="n">
-        <v>6716177</v>
+        <v>6716244</v>
       </c>
       <c r="S25" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3602,27 +3458,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-08-09</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>19:13</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-08-09</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>19:13</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>2 stjälkar</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3649,10 +3500,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127350965</v>
+        <v>130016904</v>
       </c>
       <c r="B26" t="n">
-        <v>98470</v>
+        <v>98920</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3679,7 +3530,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3689,17 +3540,17 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Hundviken, Hundviken, Dlr</t>
+          <t>Hundviken, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>525685</v>
+        <v>525602</v>
       </c>
       <c r="R26" t="n">
-        <v>6716229</v>
+        <v>6716070</v>
       </c>
       <c r="S26" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3723,27 +3574,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-08-09</t>
+          <t>2025-12-07</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>18:49</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-08-09</t>
+          <t>2025-12-07</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>18:49</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>1 stjälke</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3770,32 +3616,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129339939</v>
+        <v>130022082</v>
       </c>
       <c r="B27" t="n">
-        <v>92913</v>
+        <v>56758</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5966</v>
+        <v>208255</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Zootoca vivipara</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Jacquin, 1787)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3803,19 +3649,28 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Hundviken, Hundviken, Dlr</t>
+          <t>Intill väg, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>525799</v>
+        <v>525632</v>
       </c>
       <c r="R27" t="n">
-        <v>6716284</v>
+        <v>6716152</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3839,27 +3694,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>11:34</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>11:34</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Med tall</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3868,77 +3708,84 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Milada Alexandersson</t>
+          <t>Daniel Alexandersson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Milada Alexandersson</t>
+          <t>Daniel Alexandersson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129340627</v>
+        <v>129731617</v>
       </c>
       <c r="B28" t="n">
-        <v>98774</v>
+        <v>57684</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>100137</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Slaguggla</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Strix uralensis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Pallas, 1771</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>rastande</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Hundviken, Hundviken, Dlr</t>
+          <t>Stråtenbo 62, Stråtenbo, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>525709</v>
+        <v>525535</v>
       </c>
       <c r="R28" t="n">
-        <v>6716198</v>
+        <v>6716136</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3965,22 +3812,17 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>11:55</t>
+          <t>2025-05-15</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>11:55</t>
+          <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Vuxen slaguggla på besök från närliggande boplats</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3995,22 +3837,26 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Milada Alexandersson</t>
+          <t>Kenneth Smith</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Milada Alexandersson</t>
-        </is>
-      </c>
-      <c r="AY28" t="inlineStr"/>
+          <t>Kenneth Smith</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>Privat inventering</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129339605</v>
+        <v>130044230</v>
       </c>
       <c r="B29" t="n">
-        <v>8450</v>
+        <v>58688</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4018,42 +3864,50 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>106545</v>
+        <v>208249</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Hundviken, Hundviken, Dlr</t>
+          <t>Intill väg, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>525780</v>
+        <v>525653</v>
       </c>
       <c r="R29" t="n">
-        <v>6716226</v>
+        <v>6716143</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4077,22 +3931,17 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>11:15</t>
+          <t>2025-08-09</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>11:15</t>
+          <t>2025-08-09</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Stor för att vara vanlig groda. Närmast paddstorlek.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4101,80 +3950,70 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Milada Alexandersson</t>
+          <t>Daniel Alexandersson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Milada Alexandersson</t>
+          <t>Daniel Alexandersson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129338657</v>
+        <v>130125217</v>
       </c>
       <c r="B30" t="n">
-        <v>98774</v>
+        <v>78583</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>6437</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Hundviken, Hundviken, Dlr</t>
+          <t>Hundviken, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>525677</v>
+        <v>525602</v>
       </c>
       <c r="R30" t="n">
-        <v>6716163</v>
+        <v>6716070</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4198,27 +4037,27 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-12-14</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-12-14</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>1 överblommad</t>
+          <t>På död högstubbe av tall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4227,6 +4066,7 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -4245,57 +4085,55 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129339191</v>
+        <v>130158729</v>
       </c>
       <c r="B31" t="n">
-        <v>98774</v>
+        <v>79204</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6434</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Hundviken, Hundviken, Dlr</t>
+          <t>Hundviken, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
         <v>525746</v>
       </c>
       <c r="R31" t="n">
-        <v>6716215</v>
+        <v>6716214</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4319,22 +4157,17 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>10:59</t>
+          <t>2025-12-07</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>10:59</t>
+          <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Flertalet observeras på tallar som nyligen blåst omkull. Möjliggör inspektion längs hela trädens längd. Extra intressant fynd då arten indikerar äldre, skyddsvärd skog söder om naturliga norrlandsgränsen.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4343,80 +4176,71 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Milada Alexandersson</t>
+          <t>Daniel Alexandersson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Milada Alexandersson</t>
+          <t>Daniel Alexandersson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129339551</v>
+        <v>130044041</v>
       </c>
       <c r="B32" t="n">
-        <v>98774</v>
+        <v>97797</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Hundviken, Hundviken, Dlr</t>
+          <t>Hundviken, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>525769</v>
+        <v>525776</v>
       </c>
       <c r="R32" t="n">
-        <v>6716224</v>
+        <v>6716252</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4440,22 +4264,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>11:12</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>11:12</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4464,2094 +4278,22 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Milada Alexandersson</t>
+          <t>Daniel Alexandersson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Milada Alexandersson</t>
+          <t>Daniel Alexandersson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>129338511</v>
-      </c>
-      <c r="B33" t="n">
-        <v>98774</v>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E33" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>Hundviken, Hundviken, Dlr</t>
-        </is>
-      </c>
-      <c r="Q33" t="n">
-        <v>525680</v>
-      </c>
-      <c r="R33" t="n">
-        <v>6716143</v>
-      </c>
-      <c r="S33" t="n">
-        <v>10</v>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>Falun</t>
-        </is>
-      </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W33" t="inlineStr">
-        <is>
-          <t>Aspeboda</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>2025-10-26</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>10:31</t>
-        </is>
-      </c>
-      <c r="AA33" t="inlineStr">
-        <is>
-          <t>2025-10-26</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>10:31</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ca 20 bladrosetter 1 överblommade</t>
-        </is>
-      </c>
-      <c r="AD33" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE33" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG33" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT33" t="inlineStr"/>
-      <c r="AW33" t="inlineStr">
-        <is>
-          <t>Milada Alexandersson</t>
-        </is>
-      </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>Milada Alexandersson</t>
-        </is>
-      </c>
-      <c r="AY33" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>129338899</v>
-      </c>
-      <c r="B34" t="n">
-        <v>98774</v>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E34" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>Hundviken, Hundviken, Dlr</t>
-        </is>
-      </c>
-      <c r="Q34" t="n">
-        <v>525712</v>
-      </c>
-      <c r="R34" t="n">
-        <v>6716201</v>
-      </c>
-      <c r="S34" t="n">
-        <v>10</v>
-      </c>
-      <c r="T34" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U34" t="inlineStr">
-        <is>
-          <t>Falun</t>
-        </is>
-      </c>
-      <c r="V34" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W34" t="inlineStr">
-        <is>
-          <t>Aspeboda</t>
-        </is>
-      </c>
-      <c r="Y34" t="inlineStr">
-        <is>
-          <t>2025-10-26</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>10:50</t>
-        </is>
-      </c>
-      <c r="AA34" t="inlineStr">
-        <is>
-          <t>2025-10-26</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>10:50</t>
-        </is>
-      </c>
-      <c r="AD34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT34" t="inlineStr"/>
-      <c r="AW34" t="inlineStr">
-        <is>
-          <t>Milada Alexandersson</t>
-        </is>
-      </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>Milada Alexandersson</t>
-        </is>
-      </c>
-      <c r="AY34" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>129339499</v>
-      </c>
-      <c r="B35" t="n">
-        <v>98774</v>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E35" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>Hundviken, Hundviken, Dlr</t>
-        </is>
-      </c>
-      <c r="Q35" t="n">
-        <v>525771</v>
-      </c>
-      <c r="R35" t="n">
-        <v>6716245</v>
-      </c>
-      <c r="S35" t="n">
-        <v>10</v>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>Falun</t>
-        </is>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W35" t="inlineStr">
-        <is>
-          <t>Aspeboda</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>2025-10-26</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>11:09</t>
-        </is>
-      </c>
-      <c r="AA35" t="inlineStr">
-        <is>
-          <t>2025-10-26</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>11:09</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Spridda över ca 0,5 m2</t>
-        </is>
-      </c>
-      <c r="AD35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT35" t="inlineStr"/>
-      <c r="AW35" t="inlineStr">
-        <is>
-          <t>Milada Alexandersson</t>
-        </is>
-      </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>Milada Alexandersson</t>
-        </is>
-      </c>
-      <c r="AY35" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>129340696</v>
-      </c>
-      <c r="B36" t="n">
-        <v>98774</v>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E36" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>Hundviken, Hundviken, Dlr</t>
-        </is>
-      </c>
-      <c r="Q36" t="n">
-        <v>525672</v>
-      </c>
-      <c r="R36" t="n">
-        <v>6716190</v>
-      </c>
-      <c r="S36" t="n">
-        <v>10</v>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>Falun</t>
-        </is>
-      </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W36" t="inlineStr">
-        <is>
-          <t>Aspeboda</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>2025-10-26</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>11:59</t>
-        </is>
-      </c>
-      <c r="AA36" t="inlineStr">
-        <is>
-          <t>2025-10-26</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>11:59</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>På stenblock! 2 överblommade</t>
-        </is>
-      </c>
-      <c r="AD36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT36" t="inlineStr"/>
-      <c r="AW36" t="inlineStr">
-        <is>
-          <t>Milada Alexandersson</t>
-        </is>
-      </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>Milada Alexandersson</t>
-        </is>
-      </c>
-      <c r="AY36" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>129338834</v>
-      </c>
-      <c r="B37" t="n">
-        <v>98774</v>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E37" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>Hundviken, Hundviken, Dlr</t>
-        </is>
-      </c>
-      <c r="Q37" t="n">
-        <v>525715</v>
-      </c>
-      <c r="R37" t="n">
-        <v>6716181</v>
-      </c>
-      <c r="S37" t="n">
-        <v>10</v>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>Falun</t>
-        </is>
-      </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>Aspeboda</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>2025-10-26</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>10:47</t>
-        </is>
-      </c>
-      <c r="AA37" t="inlineStr">
-        <is>
-          <t>2025-10-26</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>10:47</t>
-        </is>
-      </c>
-      <c r="AD37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT37" t="inlineStr"/>
-      <c r="AW37" t="inlineStr">
-        <is>
-          <t>Milada Alexandersson</t>
-        </is>
-      </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>Milada Alexandersson</t>
-        </is>
-      </c>
-      <c r="AY37" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>129338590</v>
-      </c>
-      <c r="B38" t="n">
-        <v>98774</v>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E38" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>Hundviken, Hundviken, Dlr</t>
-        </is>
-      </c>
-      <c r="Q38" t="n">
-        <v>525673</v>
-      </c>
-      <c r="R38" t="n">
-        <v>6716152</v>
-      </c>
-      <c r="S38" t="n">
-        <v>1</v>
-      </c>
-      <c r="T38" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U38" t="inlineStr">
-        <is>
-          <t>Falun</t>
-        </is>
-      </c>
-      <c r="V38" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W38" t="inlineStr">
-        <is>
-          <t>Aspeboda</t>
-        </is>
-      </c>
-      <c r="Y38" t="inlineStr">
-        <is>
-          <t>2025-10-26</t>
-        </is>
-      </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>10:35</t>
-        </is>
-      </c>
-      <c r="AA38" t="inlineStr">
-        <is>
-          <t>2025-10-26</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>10:35</t>
-        </is>
-      </c>
-      <c r="AD38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT38" t="inlineStr"/>
-      <c r="AW38" t="inlineStr">
-        <is>
-          <t>Milada Alexandersson</t>
-        </is>
-      </c>
-      <c r="AX38" t="inlineStr">
-        <is>
-          <t>Milada Alexandersson</t>
-        </is>
-      </c>
-      <c r="AY38" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>129727312</v>
-      </c>
-      <c r="B39" t="n">
-        <v>58600</v>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E39" t="n">
-        <v>208250</v>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Åkergroda</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>Rana arvalis</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Nilsson, 1842</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>Åkergroda, Dlr</t>
-        </is>
-      </c>
-      <c r="Q39" t="n">
-        <v>525655</v>
-      </c>
-      <c r="R39" t="n">
-        <v>6716145</v>
-      </c>
-      <c r="S39" t="n">
-        <v>10</v>
-      </c>
-      <c r="T39" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U39" t="inlineStr">
-        <is>
-          <t>Falun</t>
-        </is>
-      </c>
-      <c r="V39" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W39" t="inlineStr">
-        <is>
-          <t>Aspeboda</t>
-        </is>
-      </c>
-      <c r="Y39" t="inlineStr">
-        <is>
-          <t>2025-08-17</t>
-        </is>
-      </c>
-      <c r="AA39" t="inlineStr">
-        <is>
-          <t>2025-08-17</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Fotad och eftergranskad av grodexpert</t>
-        </is>
-      </c>
-      <c r="AD39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF39" t="inlineStr"/>
-      <c r="AG39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT39" t="inlineStr"/>
-      <c r="AW39" t="inlineStr">
-        <is>
-          <t>Milada Alexandersson</t>
-        </is>
-      </c>
-      <c r="AX39" t="inlineStr">
-        <is>
-          <t>Milada Alexandersson</t>
-        </is>
-      </c>
-      <c r="AY39" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>129747025</v>
-      </c>
-      <c r="B40" t="n">
-        <v>57581</v>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E40" t="n">
-        <v>102621</v>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Sparvuggla</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>Glaucidium passerinum</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="P40" t="inlineStr">
-        <is>
-          <t>Stående död tall, Dlr</t>
-        </is>
-      </c>
-      <c r="Q40" t="n">
-        <v>525786</v>
-      </c>
-      <c r="R40" t="n">
-        <v>6716281</v>
-      </c>
-      <c r="S40" t="n">
-        <v>10</v>
-      </c>
-      <c r="T40" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U40" t="inlineStr">
-        <is>
-          <t>Falun</t>
-        </is>
-      </c>
-      <c r="V40" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W40" t="inlineStr">
-        <is>
-          <t>Aspeboda</t>
-        </is>
-      </c>
-      <c r="Y40" t="inlineStr">
-        <is>
-          <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>14:22</t>
-        </is>
-      </c>
-      <c r="AA40" t="inlineStr">
-        <is>
-          <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>14:22</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Sitter på toppen av en gran och bevakar.</t>
-        </is>
-      </c>
-      <c r="AD40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT40" t="inlineStr"/>
-      <c r="AW40" t="inlineStr">
-        <is>
-          <t>Milada Alexandersson</t>
-        </is>
-      </c>
-      <c r="AX40" t="inlineStr">
-        <is>
-          <t>Milada Alexandersson</t>
-        </is>
-      </c>
-      <c r="AY40" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>129979175</v>
-      </c>
-      <c r="B41" t="n">
-        <v>57898</v>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E41" t="n">
-        <v>103020</v>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Entita</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>Poecile palustris</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>Stående död tall, Dlr</t>
-        </is>
-      </c>
-      <c r="Q41" t="n">
-        <v>525766</v>
-      </c>
-      <c r="R41" t="n">
-        <v>6716251</v>
-      </c>
-      <c r="S41" t="n">
-        <v>5</v>
-      </c>
-      <c r="T41" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U41" t="inlineStr">
-        <is>
-          <t>Falun</t>
-        </is>
-      </c>
-      <c r="V41" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W41" t="inlineStr">
-        <is>
-          <t>Aspeboda</t>
-        </is>
-      </c>
-      <c r="Y41" t="inlineStr">
-        <is>
-          <t>2025-04-11</t>
-        </is>
-      </c>
-      <c r="AA41" t="inlineStr">
-        <is>
-          <t>2025-04-11</t>
-        </is>
-      </c>
-      <c r="AD41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT41" t="inlineStr"/>
-      <c r="AW41" t="inlineStr">
-        <is>
-          <t>Milada Alexandersson</t>
-        </is>
-      </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>Milada Alexandersson</t>
-        </is>
-      </c>
-      <c r="AY41" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>129979188</v>
-      </c>
-      <c r="B42" t="n">
-        <v>57738</v>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E42" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="P42" t="inlineStr">
-        <is>
-          <t>Stående död tall, "smedjor", Stående död tall, "smedjor", Dlr</t>
-        </is>
-      </c>
-      <c r="Q42" t="n">
-        <v>525724</v>
-      </c>
-      <c r="R42" t="n">
-        <v>6716195</v>
-      </c>
-      <c r="S42" t="n">
-        <v>5</v>
-      </c>
-      <c r="T42" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U42" t="inlineStr">
-        <is>
-          <t>Falun</t>
-        </is>
-      </c>
-      <c r="V42" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W42" t="inlineStr">
-        <is>
-          <t>Aspeboda</t>
-        </is>
-      </c>
-      <c r="Y42" t="inlineStr">
-        <is>
-          <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
-      <c r="AA42" t="inlineStr">
-        <is>
-          <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
-      <c r="AD42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT42" t="inlineStr"/>
-      <c r="AW42" t="inlineStr">
-        <is>
-          <t>Milada Alexandersson</t>
-        </is>
-      </c>
-      <c r="AX42" t="inlineStr">
-        <is>
-          <t>Milada Alexandersson</t>
-        </is>
-      </c>
-      <c r="AY42" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>129979221</v>
-      </c>
-      <c r="B43" t="n">
-        <v>57733</v>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E43" t="n">
-        <v>100110</v>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Gråspett</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>Picus canus</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>J.F. Gmelin, 1788</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="P43" t="inlineStr">
-        <is>
-          <t>Stående död tall, Stående död tall, Dlr</t>
-        </is>
-      </c>
-      <c r="Q43" t="n">
-        <v>525782</v>
-      </c>
-      <c r="R43" t="n">
-        <v>6716244</v>
-      </c>
-      <c r="S43" t="n">
-        <v>5</v>
-      </c>
-      <c r="T43" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U43" t="inlineStr">
-        <is>
-          <t>Falun</t>
-        </is>
-      </c>
-      <c r="V43" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W43" t="inlineStr">
-        <is>
-          <t>Aspeboda</t>
-        </is>
-      </c>
-      <c r="Y43" t="inlineStr">
-        <is>
-          <t>2025-10-26</t>
-        </is>
-      </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
-      <c r="AA43" t="inlineStr">
-        <is>
-          <t>2025-10-26</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
-      <c r="AD43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT43" t="inlineStr"/>
-      <c r="AW43" t="inlineStr">
-        <is>
-          <t>Milada Alexandersson</t>
-        </is>
-      </c>
-      <c r="AX43" t="inlineStr">
-        <is>
-          <t>Milada Alexandersson</t>
-        </is>
-      </c>
-      <c r="AY43" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" t="n">
-        <v>130022082</v>
-      </c>
-      <c r="B44" t="n">
-        <v>56673</v>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E44" t="n">
-        <v>208255</v>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Skogsödla</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>Zootoca vivipara</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>(Jacquin, 1787)</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
-      <c r="P44" t="inlineStr">
-        <is>
-          <t>Intill väg, Dlr</t>
-        </is>
-      </c>
-      <c r="Q44" t="n">
-        <v>525632</v>
-      </c>
-      <c r="R44" t="n">
-        <v>6716152</v>
-      </c>
-      <c r="S44" t="n">
-        <v>5</v>
-      </c>
-      <c r="T44" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U44" t="inlineStr">
-        <is>
-          <t>Falun</t>
-        </is>
-      </c>
-      <c r="V44" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W44" t="inlineStr">
-        <is>
-          <t>Aspeboda</t>
-        </is>
-      </c>
-      <c r="Y44" t="inlineStr">
-        <is>
-          <t>2025-09-06</t>
-        </is>
-      </c>
-      <c r="AA44" t="inlineStr">
-        <is>
-          <t>2025-09-06</t>
-        </is>
-      </c>
-      <c r="AD44" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE44" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF44" t="inlineStr"/>
-      <c r="AG44" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT44" t="inlineStr"/>
-      <c r="AW44" t="inlineStr">
-        <is>
-          <t>Daniel Alexandersson</t>
-        </is>
-      </c>
-      <c r="AX44" t="inlineStr">
-        <is>
-          <t>Daniel Alexandersson</t>
-        </is>
-      </c>
-      <c r="AY44" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" t="n">
-        <v>130016904</v>
-      </c>
-      <c r="B45" t="n">
-        <v>98833</v>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E45" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="P45" t="inlineStr">
-        <is>
-          <t>Hundviken, Dlr</t>
-        </is>
-      </c>
-      <c r="Q45" t="n">
-        <v>525602</v>
-      </c>
-      <c r="R45" t="n">
-        <v>6716070</v>
-      </c>
-      <c r="S45" t="n">
-        <v>5</v>
-      </c>
-      <c r="T45" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U45" t="inlineStr">
-        <is>
-          <t>Falun</t>
-        </is>
-      </c>
-      <c r="V45" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W45" t="inlineStr">
-        <is>
-          <t>Aspeboda</t>
-        </is>
-      </c>
-      <c r="Y45" t="inlineStr">
-        <is>
-          <t>2025-12-07</t>
-        </is>
-      </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>13:58</t>
-        </is>
-      </c>
-      <c r="AA45" t="inlineStr">
-        <is>
-          <t>2025-12-07</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>13:58</t>
-        </is>
-      </c>
-      <c r="AD45" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE45" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG45" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT45" t="inlineStr"/>
-      <c r="AW45" t="inlineStr">
-        <is>
-          <t>Milada Alexandersson</t>
-        </is>
-      </c>
-      <c r="AX45" t="inlineStr">
-        <is>
-          <t>Milada Alexandersson</t>
-        </is>
-      </c>
-      <c r="AY45" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" t="n">
-        <v>129731617</v>
-      </c>
-      <c r="B46" t="n">
-        <v>57599</v>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E46" t="n">
-        <v>100137</v>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>Slaguggla</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>Strix uralensis</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Pallas, 1771</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>rastande</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
-      <c r="P46" t="inlineStr">
-        <is>
-          <t>Stråtenbo 62, Stråtenbo, Dlr</t>
-        </is>
-      </c>
-      <c r="Q46" t="n">
-        <v>525535</v>
-      </c>
-      <c r="R46" t="n">
-        <v>6716136</v>
-      </c>
-      <c r="S46" t="n">
-        <v>10</v>
-      </c>
-      <c r="T46" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U46" t="inlineStr">
-        <is>
-          <t>Falun</t>
-        </is>
-      </c>
-      <c r="V46" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W46" t="inlineStr">
-        <is>
-          <t>Aspeboda</t>
-        </is>
-      </c>
-      <c r="Y46" t="inlineStr">
-        <is>
-          <t>2025-05-15</t>
-        </is>
-      </c>
-      <c r="AA46" t="inlineStr">
-        <is>
-          <t>2025-05-15</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Vuxen slaguggla på besök från närliggande boplats</t>
-        </is>
-      </c>
-      <c r="AD46" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE46" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG46" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT46" t="inlineStr"/>
-      <c r="AW46" t="inlineStr">
-        <is>
-          <t>Kenneth Smith</t>
-        </is>
-      </c>
-      <c r="AX46" t="inlineStr">
-        <is>
-          <t>Kenneth Smith</t>
-        </is>
-      </c>
-      <c r="AY46" t="inlineStr">
-        <is>
-          <t>Privat inventering</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
-        <v>130044230</v>
-      </c>
-      <c r="B47" t="n">
-        <v>58603</v>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E47" t="n">
-        <v>208249</v>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>Vanlig groda</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>Rana temporaria</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
-      <c r="P47" t="inlineStr">
-        <is>
-          <t>Intill väg, Dlr</t>
-        </is>
-      </c>
-      <c r="Q47" t="n">
-        <v>525653</v>
-      </c>
-      <c r="R47" t="n">
-        <v>6716143</v>
-      </c>
-      <c r="S47" t="n">
-        <v>5</v>
-      </c>
-      <c r="T47" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U47" t="inlineStr">
-        <is>
-          <t>Falun</t>
-        </is>
-      </c>
-      <c r="V47" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W47" t="inlineStr">
-        <is>
-          <t>Aspeboda</t>
-        </is>
-      </c>
-      <c r="Y47" t="inlineStr">
-        <is>
-          <t>2025-08-09</t>
-        </is>
-      </c>
-      <c r="AA47" t="inlineStr">
-        <is>
-          <t>2025-08-09</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Stor för att vara vanlig groda. Närmast paddstorlek.</t>
-        </is>
-      </c>
-      <c r="AD47" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE47" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF47" t="inlineStr"/>
-      <c r="AG47" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT47" t="inlineStr"/>
-      <c r="AW47" t="inlineStr">
-        <is>
-          <t>Daniel Alexandersson</t>
-        </is>
-      </c>
-      <c r="AX47" t="inlineStr">
-        <is>
-          <t>Daniel Alexandersson</t>
-        </is>
-      </c>
-      <c r="AY47" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>130125217</v>
-      </c>
-      <c r="B48" t="n">
-        <v>78498</v>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E48" t="n">
-        <v>6437</v>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>Blanksvart spiklav</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>Calicium denigratum</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
-      <c r="P48" t="inlineStr">
-        <is>
-          <t>Hundviken, Dlr</t>
-        </is>
-      </c>
-      <c r="Q48" t="n">
-        <v>525602</v>
-      </c>
-      <c r="R48" t="n">
-        <v>6716070</v>
-      </c>
-      <c r="S48" t="n">
-        <v>5</v>
-      </c>
-      <c r="T48" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U48" t="inlineStr">
-        <is>
-          <t>Falun</t>
-        </is>
-      </c>
-      <c r="V48" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W48" t="inlineStr">
-        <is>
-          <t>Aspeboda</t>
-        </is>
-      </c>
-      <c r="Y48" t="inlineStr">
-        <is>
-          <t>2025-12-14</t>
-        </is>
-      </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>13:37</t>
-        </is>
-      </c>
-      <c r="AA48" t="inlineStr">
-        <is>
-          <t>2025-12-14</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>13:37</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>På död högstubbe av tall</t>
-        </is>
-      </c>
-      <c r="AD48" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE48" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF48" t="inlineStr"/>
-      <c r="AG48" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT48" t="inlineStr"/>
-      <c r="AW48" t="inlineStr">
-        <is>
-          <t>Milada Alexandersson</t>
-        </is>
-      </c>
-      <c r="AX48" t="inlineStr">
-        <is>
-          <t>Milada Alexandersson</t>
-        </is>
-      </c>
-      <c r="AY48" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
-        <v>130158729</v>
-      </c>
-      <c r="B49" t="n">
-        <v>79119</v>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E49" t="n">
-        <v>6434</v>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>Nästlav</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>Bryoria furcellata</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
-      <c r="P49" t="inlineStr">
-        <is>
-          <t>Hundviken, Dlr</t>
-        </is>
-      </c>
-      <c r="Q49" t="n">
-        <v>525746</v>
-      </c>
-      <c r="R49" t="n">
-        <v>6716214</v>
-      </c>
-      <c r="S49" t="n">
-        <v>5</v>
-      </c>
-      <c r="T49" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U49" t="inlineStr">
-        <is>
-          <t>Falun</t>
-        </is>
-      </c>
-      <c r="V49" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W49" t="inlineStr">
-        <is>
-          <t>Aspeboda</t>
-        </is>
-      </c>
-      <c r="Y49" t="inlineStr">
-        <is>
-          <t>2025-12-07</t>
-        </is>
-      </c>
-      <c r="AA49" t="inlineStr">
-        <is>
-          <t>2025-12-07</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Flertalet observeras på tallar som nyligen blåst omkull. Möjliggör inspektion längs hela trädens längd. Extra intressant fynd då arten indikerar äldre, skyddsvärd skog söder om naturliga norrlandsgränsen.</t>
-        </is>
-      </c>
-      <c r="AD49" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE49" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF49" t="inlineStr"/>
-      <c r="AG49" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT49" t="inlineStr"/>
-      <c r="AW49" t="inlineStr">
-        <is>
-          <t>Daniel Alexandersson</t>
-        </is>
-      </c>
-      <c r="AX49" t="inlineStr">
-        <is>
-          <t>Daniel Alexandersson</t>
-        </is>
-      </c>
-      <c r="AY49" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
-        <v>130044041</v>
-      </c>
-      <c r="B50" t="n">
-        <v>97710</v>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E50" t="n">
-        <v>221941</v>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>Plattlummer</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>Lycopodium complanatum</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
-      <c r="P50" t="inlineStr">
-        <is>
-          <t>Hundviken, Dlr</t>
-        </is>
-      </c>
-      <c r="Q50" t="n">
-        <v>525776</v>
-      </c>
-      <c r="R50" t="n">
-        <v>6716252</v>
-      </c>
-      <c r="S50" t="n">
-        <v>25</v>
-      </c>
-      <c r="T50" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U50" t="inlineStr">
-        <is>
-          <t>Falun</t>
-        </is>
-      </c>
-      <c r="V50" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W50" t="inlineStr">
-        <is>
-          <t>Aspeboda</t>
-        </is>
-      </c>
-      <c r="Y50" t="inlineStr">
-        <is>
-          <t>2025-08-04</t>
-        </is>
-      </c>
-      <c r="AA50" t="inlineStr">
-        <is>
-          <t>2025-08-04</t>
-        </is>
-      </c>
-      <c r="AD50" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE50" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF50" t="inlineStr"/>
-      <c r="AG50" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT50" t="inlineStr"/>
-      <c r="AW50" t="inlineStr">
-        <is>
-          <t>Daniel Alexandersson</t>
-        </is>
-      </c>
-      <c r="AX50" t="inlineStr">
-        <is>
-          <t>Daniel Alexandersson</t>
-        </is>
-      </c>
-      <c r="AY50" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 52871-2025 artfynd.xlsx
+++ b/artfynd/A 52871-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY32"/>
+  <dimension ref="A1:AY50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127351108</v>
+        <v>127315588</v>
       </c>
       <c r="B2" t="n">
-        <v>98470</v>
+        <v>98469</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -705,12 +705,22 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,10 +729,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>525674</v>
+        <v>525666</v>
       </c>
       <c r="R2" t="n">
-        <v>6716190</v>
+        <v>6716159</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -749,27 +759,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-08-09</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>18:56</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-08-09</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>18:56</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>1 stjälke</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127351427</v>
+        <v>127315514</v>
       </c>
       <c r="B3" t="n">
-        <v>98470</v>
+        <v>98469</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -826,12 +831,22 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -840,10 +855,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>525690</v>
+        <v>525676</v>
       </c>
       <c r="R3" t="n">
-        <v>6716183</v>
+        <v>6716168</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -870,27 +885,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-08-09</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-08-09</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>19:10</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>1 stjälke</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -917,10 +927,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127351240</v>
+        <v>127316295</v>
       </c>
       <c r="B4" t="n">
-        <v>98470</v>
+        <v>98469</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -947,7 +957,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -955,19 +965,29 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Hundviken, Hundviken, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>525680</v>
+        <v>525743</v>
       </c>
       <c r="R4" t="n">
-        <v>6716185</v>
+        <v>6716220</v>
       </c>
       <c r="S4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -991,22 +1011,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-08-09</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-08-09</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1033,10 +1053,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127351678</v>
+        <v>127314167</v>
       </c>
       <c r="B5" t="n">
-        <v>98470</v>
+        <v>98469</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1063,12 +1083,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1077,13 +1102,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>525682</v>
+        <v>525686</v>
       </c>
       <c r="R5" t="n">
-        <v>6716183</v>
+        <v>6716155</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1107,22 +1132,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-08-09</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>19:23</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-08-09</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>19:23</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1149,10 +1174,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127351377</v>
+        <v>127315222</v>
       </c>
       <c r="B6" t="n">
-        <v>98470</v>
+        <v>98469</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1179,12 +1204,22 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1193,10 +1228,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>525680</v>
+        <v>525682</v>
       </c>
       <c r="R6" t="n">
-        <v>6716172</v>
+        <v>6716184</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1223,27 +1258,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-08-09</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>19:07</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-08-09</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>19:07</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>1 stjälke</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1270,10 +1300,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127351465</v>
+        <v>127315716</v>
       </c>
       <c r="B7" t="n">
-        <v>98470</v>
+        <v>98469</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1300,12 +1330,22 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1314,10 +1354,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>525676</v>
+        <v>525670</v>
       </c>
       <c r="R7" t="n">
-        <v>6716177</v>
+        <v>6716189</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1344,27 +1384,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-08-09</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>19:13</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-08-09</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>19:13</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>2 stjälkar</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1391,10 +1426,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127350965</v>
+        <v>127316344</v>
       </c>
       <c r="B8" t="n">
-        <v>98470</v>
+        <v>98469</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1421,12 +1456,17 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1435,13 +1475,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>525685</v>
+        <v>525736</v>
       </c>
       <c r="R8" t="n">
-        <v>6716229</v>
+        <v>6716217</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1465,27 +1505,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-08-09</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>18:49</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-08-09</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>18:49</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>1 stjälke</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1512,32 +1547,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129339939</v>
+        <v>127316136</v>
       </c>
       <c r="B9" t="n">
-        <v>92913</v>
+        <v>98469</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5966</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1545,19 +1580,34 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hundviken, Hundviken, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>525799</v>
+        <v>525712</v>
       </c>
       <c r="R9" t="n">
-        <v>6716284</v>
+        <v>6716193</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1581,27 +1631,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:34</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Med tall</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1628,10 +1673,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129340627</v>
+        <v>127316228</v>
       </c>
       <c r="B10" t="n">
-        <v>98774</v>
+        <v>98469</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1658,17 +1703,22 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1677,13 +1727,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>525709</v>
+        <v>525740</v>
       </c>
       <c r="R10" t="n">
-        <v>6716198</v>
+        <v>6716244</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1707,22 +1757,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1749,38 +1799,52 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129339605</v>
+        <v>127314992</v>
       </c>
       <c r="B11" t="n">
-        <v>8450</v>
+        <v>98469</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1789,13 +1853,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>525780</v>
+        <v>525694</v>
       </c>
       <c r="R11" t="n">
-        <v>6716226</v>
+        <v>6716178</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1819,22 +1883,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1861,10 +1925,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129338657</v>
+        <v>127316105</v>
       </c>
       <c r="B12" t="n">
-        <v>98774</v>
+        <v>98469</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1891,17 +1955,22 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1910,13 +1979,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>525677</v>
+        <v>525712</v>
       </c>
       <c r="R12" t="n">
-        <v>6716163</v>
+        <v>6716192</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1940,27 +2009,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:38</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>1 överblommad</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1987,10 +2051,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129339191</v>
+        <v>127316409</v>
       </c>
       <c r="B13" t="n">
-        <v>98774</v>
+        <v>98469</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2017,12 +2081,22 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2031,13 +2105,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>525746</v>
+        <v>525735</v>
       </c>
       <c r="R13" t="n">
-        <v>6716215</v>
+        <v>6716213</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2061,22 +2135,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2103,10 +2177,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129339551</v>
+        <v>127315619</v>
       </c>
       <c r="B14" t="n">
-        <v>98774</v>
+        <v>98469</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2133,17 +2207,22 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2152,13 +2231,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>525769</v>
+        <v>525656</v>
       </c>
       <c r="R14" t="n">
-        <v>6716224</v>
+        <v>6716166</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2182,22 +2261,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2224,10 +2303,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129338511</v>
+        <v>127315460</v>
       </c>
       <c r="B15" t="n">
-        <v>98774</v>
+        <v>98469</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2254,12 +2333,22 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2268,13 +2357,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>525680</v>
+        <v>525688</v>
       </c>
       <c r="R15" t="n">
-        <v>6716143</v>
+        <v>6716179</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2298,27 +2387,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:31</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ca 20 bladrosetter 1 överblommade</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2345,10 +2429,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129338899</v>
+        <v>127315125</v>
       </c>
       <c r="B16" t="n">
-        <v>98774</v>
+        <v>98469</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2375,17 +2459,22 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2394,13 +2483,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>525712</v>
+        <v>525684</v>
       </c>
       <c r="R16" t="n">
-        <v>6716201</v>
+        <v>6716162</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2424,22 +2513,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2466,10 +2555,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129339499</v>
+        <v>127316162</v>
       </c>
       <c r="B17" t="n">
-        <v>98774</v>
+        <v>98469</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2496,17 +2585,22 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2515,13 +2609,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>525771</v>
+        <v>525752</v>
       </c>
       <c r="R17" t="n">
-        <v>6716245</v>
+        <v>6716206</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2545,27 +2639,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:09</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Spridda över ca 0,5 m2</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2592,10 +2681,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129340696</v>
+        <v>127313556</v>
       </c>
       <c r="B18" t="n">
-        <v>98774</v>
+        <v>98469</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2622,7 +2711,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2630,19 +2719,29 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Hundviken, Hundviken, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>525672</v>
+        <v>525685</v>
       </c>
       <c r="R18" t="n">
-        <v>6716190</v>
+        <v>6716175</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2666,27 +2765,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:59</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>På stenblock! 2 överblommade</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2713,10 +2807,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129338834</v>
+        <v>127314541</v>
       </c>
       <c r="B19" t="n">
-        <v>98774</v>
+        <v>98469</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2743,12 +2837,22 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2757,13 +2861,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>525715</v>
+        <v>525690</v>
       </c>
       <c r="R19" t="n">
-        <v>6716181</v>
+        <v>6716175</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2787,22 +2891,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2829,10 +2933,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129338590</v>
+        <v>127351108</v>
       </c>
       <c r="B20" t="n">
-        <v>98774</v>
+        <v>98470</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2859,12 +2963,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2873,10 +2977,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>525673</v>
+        <v>525674</v>
       </c>
       <c r="R20" t="n">
-        <v>6716152</v>
+        <v>6716190</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2903,22 +3007,27 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-08-09</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>18:56</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-08-09</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>18:56</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>1 stjälke</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2945,57 +3054,57 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129727312</v>
+        <v>127351427</v>
       </c>
       <c r="B21" t="n">
-        <v>58600</v>
+        <v>98470</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>208250</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Åkergroda, Dlr</t>
+          <t>Hundviken, Hundviken, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>525655</v>
+        <v>525690</v>
       </c>
       <c r="R21" t="n">
-        <v>6716145</v>
+        <v>6716183</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3019,17 +3128,27 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-08-17</t>
+          <t>2025-08-09</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>19:10</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-08-17</t>
+          <t>2025-08-09</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>19:10</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Fotad och eftergranskad av grodexpert</t>
+          <t>1 stjälke</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3038,7 +3157,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3057,53 +3175,57 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129747025</v>
+        <v>127351240</v>
       </c>
       <c r="B22" t="n">
-        <v>57581</v>
+        <v>98470</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>102621</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Stående död tall, Dlr</t>
+          <t>Hundviken, Hundviken, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>525786</v>
+        <v>525680</v>
       </c>
       <c r="R22" t="n">
-        <v>6716281</v>
+        <v>6716185</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3127,27 +3249,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-08-09</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-08-09</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:22</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Sitter på toppen av en gran och bevakar.</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3174,50 +3291,54 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129979175</v>
+        <v>127351678</v>
       </c>
       <c r="B23" t="n">
-        <v>57983</v>
+        <v>98470</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103020</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Stående död tall, Dlr</t>
+          <t>Hundviken, Hundviken, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>525766</v>
+        <v>525682</v>
       </c>
       <c r="R23" t="n">
-        <v>6716251</v>
+        <v>6716183</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3244,12 +3365,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-04-11</t>
+          <t>2025-08-09</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>19:23</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-04-11</t>
+          <t>2025-08-09</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>19:23</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3276,53 +3407,57 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129979188</v>
+        <v>127351377</v>
       </c>
       <c r="B24" t="n">
-        <v>57823</v>
+        <v>98470</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Stående död tall, "smedjor", Stående död tall, "smedjor", Dlr</t>
+          <t>Hundviken, Hundviken, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>525724</v>
+        <v>525680</v>
       </c>
       <c r="R24" t="n">
-        <v>6716195</v>
+        <v>6716172</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3346,22 +3481,27 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-08-09</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>19:07</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-08-09</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>19:07</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>1 stjälke</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3388,53 +3528,57 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129979221</v>
+        <v>127351465</v>
       </c>
       <c r="B25" t="n">
-        <v>57818</v>
+        <v>98470</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100110</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Stående död tall, Stående död tall, Dlr</t>
+          <t>Hundviken, Hundviken, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>525782</v>
+        <v>525676</v>
       </c>
       <c r="R25" t="n">
-        <v>6716244</v>
+        <v>6716177</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3458,22 +3602,27 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-08-09</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>19:13</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-08-09</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>19:13</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>2 stjälkar</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3500,10 +3649,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130016904</v>
+        <v>127350965</v>
       </c>
       <c r="B26" t="n">
-        <v>98920</v>
+        <v>98470</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3530,7 +3679,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3540,17 +3689,17 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Hundviken, Dlr</t>
+          <t>Hundviken, Hundviken, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>525602</v>
+        <v>525685</v>
       </c>
       <c r="R26" t="n">
-        <v>6716070</v>
+        <v>6716229</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3574,22 +3723,27 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-12-07</t>
+          <t>2025-08-09</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>18:49</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-12-07</t>
+          <t>2025-08-09</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>18:49</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>1 stjälke</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3616,32 +3770,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130022082</v>
+        <v>129339939</v>
       </c>
       <c r="B27" t="n">
-        <v>56758</v>
+        <v>92913</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>208255</v>
+        <v>5966</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Zootoca vivipara</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Jacquin, 1787)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3649,28 +3803,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Intill väg, Dlr</t>
+          <t>Hundviken, Hundviken, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>525632</v>
+        <v>525799</v>
       </c>
       <c r="R27" t="n">
-        <v>6716152</v>
+        <v>6716284</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3694,12 +3839,27 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Med tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3708,84 +3868,77 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Daniel Alexandersson</t>
+          <t>Milada Alexandersson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Daniel Alexandersson</t>
+          <t>Milada Alexandersson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129731617</v>
+        <v>129340627</v>
       </c>
       <c r="B28" t="n">
-        <v>57684</v>
+        <v>98774</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100137</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Slaguggla</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Strix uralensis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Pallas, 1771</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>rastande</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Stråtenbo 62, Stråtenbo, Dlr</t>
+          <t>Hundviken, Hundviken, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>525535</v>
+        <v>525709</v>
       </c>
       <c r="R28" t="n">
-        <v>6716136</v>
+        <v>6716198</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3812,17 +3965,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-05-15</t>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-05-15</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Vuxen slaguggla på besök från närliggande boplats</t>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3837,26 +3995,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kenneth Smith</t>
+          <t>Milada Alexandersson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kenneth Smith</t>
-        </is>
-      </c>
-      <c r="AY28" t="inlineStr">
-        <is>
-          <t>Privat inventering</t>
-        </is>
-      </c>
+          <t>Milada Alexandersson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130044230</v>
+        <v>129339605</v>
       </c>
       <c r="B29" t="n">
-        <v>58688</v>
+        <v>8450</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3864,50 +4018,42 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>208249</v>
+        <v>106545</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Intill väg, Dlr</t>
+          <t>Hundviken, Hundviken, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>525653</v>
+        <v>525780</v>
       </c>
       <c r="R29" t="n">
-        <v>6716143</v>
+        <v>6716226</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3931,17 +4077,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-08-09</t>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-08-09</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Stor för att vara vanlig groda. Närmast paddstorlek.</t>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3950,70 +4101,80 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Daniel Alexandersson</t>
+          <t>Milada Alexandersson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Daniel Alexandersson</t>
+          <t>Milada Alexandersson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130125217</v>
+        <v>129338657</v>
       </c>
       <c r="B30" t="n">
-        <v>78583</v>
+        <v>98774</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6437</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Hundviken, Dlr</t>
+          <t>Hundviken, Hundviken, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>525602</v>
+        <v>525677</v>
       </c>
       <c r="R30" t="n">
-        <v>6716070</v>
+        <v>6716163</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4037,27 +4198,27 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-12-14</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-12-14</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>På död högstubbe av tall</t>
+          <t>1 överblommad</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4066,7 +4227,6 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -4085,55 +4245,57 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130158729</v>
+        <v>129339191</v>
       </c>
       <c r="B31" t="n">
-        <v>79204</v>
+        <v>98774</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6434</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Hundviken, Dlr</t>
+          <t>Hundviken, Hundviken, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
         <v>525746</v>
       </c>
       <c r="R31" t="n">
-        <v>6716214</v>
+        <v>6716215</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4157,17 +4319,22 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-12-07</t>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-12-07</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Flertalet observeras på tallar som nyligen blåst omkull. Möjliggör inspektion längs hela trädens längd. Extra intressant fynd då arten indikerar äldre, skyddsvärd skog söder om naturliga norrlandsgränsen.</t>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4176,71 +4343,80 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Daniel Alexandersson</t>
+          <t>Milada Alexandersson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Daniel Alexandersson</t>
+          <t>Milada Alexandersson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130044041</v>
+        <v>129339551</v>
       </c>
       <c r="B32" t="n">
-        <v>97797</v>
+        <v>98774</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Hundviken, Dlr</t>
+          <t>Hundviken, Hundviken, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>525776</v>
+        <v>525769</v>
       </c>
       <c r="R32" t="n">
-        <v>6716252</v>
+        <v>6716224</v>
       </c>
       <c r="S32" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4264,12 +4440,22 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4278,22 +4464,2094 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
+          <t>Milada Alexandersson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Milada Alexandersson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>129338511</v>
+      </c>
+      <c r="B33" t="n">
+        <v>98774</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Hundviken, Hundviken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>525680</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6716143</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Aspeboda</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>10:31</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>10:31</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ca 20 bladrosetter 1 överblommade</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Milada Alexandersson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Milada Alexandersson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>129338899</v>
+      </c>
+      <c r="B34" t="n">
+        <v>98774</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Hundviken, Hundviken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>525712</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6716201</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Aspeboda</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Milada Alexandersson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Milada Alexandersson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>129339499</v>
+      </c>
+      <c r="B35" t="n">
+        <v>98774</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Hundviken, Hundviken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>525771</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6716245</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Aspeboda</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>11:09</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>11:09</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Spridda över ca 0,5 m2</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Milada Alexandersson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Milada Alexandersson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>129340696</v>
+      </c>
+      <c r="B36" t="n">
+        <v>98774</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Hundviken, Hundviken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>525672</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6716190</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Aspeboda</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>På stenblock! 2 överblommade</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Milada Alexandersson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Milada Alexandersson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>129338834</v>
+      </c>
+      <c r="B37" t="n">
+        <v>98774</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Hundviken, Hundviken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>525715</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6716181</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Aspeboda</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>10:47</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>10:47</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Milada Alexandersson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Milada Alexandersson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>129338590</v>
+      </c>
+      <c r="B38" t="n">
+        <v>98774</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Hundviken, Hundviken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>525673</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6716152</v>
+      </c>
+      <c r="S38" t="n">
+        <v>1</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Aspeboda</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Milada Alexandersson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Milada Alexandersson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>129727312</v>
+      </c>
+      <c r="B39" t="n">
+        <v>58600</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>208250</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Åkergroda</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Rana arvalis</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Nilsson, 1842</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Åkergroda, Dlr</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>525655</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6716145</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Aspeboda</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Fotad och eftergranskad av grodexpert</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Milada Alexandersson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Milada Alexandersson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>129747025</v>
+      </c>
+      <c r="B40" t="n">
+        <v>57581</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>102621</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Sparvuggla</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Glaucidium passerinum</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Stående död tall, Dlr</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>525786</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6716281</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Aspeboda</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Sitter på toppen av en gran och bevakar.</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Milada Alexandersson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Milada Alexandersson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>129979175</v>
+      </c>
+      <c r="B41" t="n">
+        <v>57983</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Stående död tall, Dlr</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>525766</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6716251</v>
+      </c>
+      <c r="S41" t="n">
+        <v>5</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Aspeboda</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Milada Alexandersson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Milada Alexandersson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>129979188</v>
+      </c>
+      <c r="B42" t="n">
+        <v>57823</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Stående död tall, "smedjor", Stående död tall, "smedjor", Dlr</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>525724</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6716195</v>
+      </c>
+      <c r="S42" t="n">
+        <v>5</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Aspeboda</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Milada Alexandersson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Milada Alexandersson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>129979221</v>
+      </c>
+      <c r="B43" t="n">
+        <v>57818</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>100110</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Gråspett</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Picus canus</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>J.F. Gmelin, 1788</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Stående död tall, Stående död tall, Dlr</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>525782</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6716244</v>
+      </c>
+      <c r="S43" t="n">
+        <v>5</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Aspeboda</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Milada Alexandersson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Milada Alexandersson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>130022082</v>
+      </c>
+      <c r="B44" t="n">
+        <v>56758</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>208255</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Skogsödla</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Zootoca vivipara</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Jacquin, 1787)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Intill väg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>525632</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6716152</v>
+      </c>
+      <c r="S44" t="n">
+        <v>5</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Aspeboda</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF44" t="inlineStr"/>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
           <t>Daniel Alexandersson</t>
         </is>
       </c>
-      <c r="AX32" t="inlineStr">
+      <c r="AX44" t="inlineStr">
         <is>
           <t>Daniel Alexandersson</t>
         </is>
       </c>
-      <c r="AY32" t="inlineStr"/>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>130016904</v>
+      </c>
+      <c r="B45" t="n">
+        <v>98920</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Hundviken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>525602</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6716070</v>
+      </c>
+      <c r="S45" t="n">
+        <v>5</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Aspeboda</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Milada Alexandersson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Milada Alexandersson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>129731617</v>
+      </c>
+      <c r="B46" t="n">
+        <v>57684</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>100137</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Slaguggla</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Strix uralensis</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Pallas, 1771</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>rastande</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Stråtenbo 62, Stråtenbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>525535</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6716136</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Aspeboda</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Vuxen slaguggla på besök från närliggande boplats</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Kenneth Smith</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Kenneth Smith</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr">
+        <is>
+          <t>Privat inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>130044230</v>
+      </c>
+      <c r="B47" t="n">
+        <v>58688</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>208249</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Vanlig groda</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Rana temporaria</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Intill väg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>525653</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6716143</v>
+      </c>
+      <c r="S47" t="n">
+        <v>5</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Aspeboda</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-08-09</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-08-09</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Stor för att vara vanlig groda. Närmast paddstorlek.</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF47" t="inlineStr"/>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Daniel Alexandersson</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Daniel Alexandersson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>130125217</v>
+      </c>
+      <c r="B48" t="n">
+        <v>78583</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Hundviken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>525602</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6716070</v>
+      </c>
+      <c r="S48" t="n">
+        <v>5</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Aspeboda</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-12-14</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>13:37</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-12-14</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>13:37</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>På död högstubbe av tall</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF48" t="inlineStr"/>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Milada Alexandersson</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Milada Alexandersson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>130158729</v>
+      </c>
+      <c r="B49" t="n">
+        <v>79204</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>6434</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Nästlav</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Bryoria furcellata</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Hundviken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>525746</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6716214</v>
+      </c>
+      <c r="S49" t="n">
+        <v>5</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Aspeboda</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Flertalet observeras på tallar som nyligen blåst omkull. Möjliggör inspektion längs hela trädens längd. Extra intressant fynd då arten indikerar äldre, skyddsvärd skog söder om naturliga norrlandsgränsen.</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF49" t="inlineStr"/>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Daniel Alexandersson</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Daniel Alexandersson</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>130044041</v>
+      </c>
+      <c r="B50" t="n">
+        <v>97797</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Hundviken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>525776</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6716252</v>
+      </c>
+      <c r="S50" t="n">
+        <v>25</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Aspeboda</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF50" t="inlineStr"/>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Daniel Alexandersson</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Daniel Alexandersson</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 52871-2025 artfynd.xlsx
+++ b/artfynd/A 52871-2025 artfynd.xlsx
@@ -6230,7 +6230,7 @@
         <v>130125217</v>
       </c>
       <c r="B48" t="n">
-        <v>78583</v>
+        <v>78586</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6346,7 +6346,7 @@
         <v>130158729</v>
       </c>
       <c r="B49" t="n">
-        <v>79204</v>
+        <v>79207</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6456,7 +6456,7 @@
         <v>130044041</v>
       </c>
       <c r="B50" t="n">
-        <v>97797</v>
+        <v>97800</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/A 52871-2025 artfynd.xlsx
+++ b/artfynd/A 52871-2025 artfynd.xlsx
@@ -6230,7 +6230,7 @@
         <v>130125217</v>
       </c>
       <c r="B48" t="n">
-        <v>78586</v>
+        <v>78612</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6346,7 +6346,7 @@
         <v>130158729</v>
       </c>
       <c r="B49" t="n">
-        <v>79207</v>
+        <v>79233</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6456,7 +6456,7 @@
         <v>130044041</v>
       </c>
       <c r="B50" t="n">
-        <v>97800</v>
+        <v>97826</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/A 52871-2025 artfynd.xlsx
+++ b/artfynd/A 52871-2025 artfynd.xlsx
@@ -6456,7 +6456,7 @@
         <v>130044041</v>
       </c>
       <c r="B50" t="n">
-        <v>97826</v>
+        <v>97827</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/A 52871-2025 artfynd.xlsx
+++ b/artfynd/A 52871-2025 artfynd.xlsx
@@ -6456,7 +6456,7 @@
         <v>130044041</v>
       </c>
       <c r="B50" t="n">
-        <v>97827</v>
+        <v>97828</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/A 52871-2025 artfynd.xlsx
+++ b/artfynd/A 52871-2025 artfynd.xlsx
@@ -6558,7 +6558,7 @@
         <v>131158283</v>
       </c>
       <c r="B51" t="n">
-        <v>58043</v>
+        <v>58045</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6672,7 +6672,7 @@
         <v>131158205</v>
       </c>
       <c r="B52" t="n">
-        <v>58043</v>
+        <v>58045</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6781,7 +6781,7 @@
         <v>131158127</v>
       </c>
       <c r="B53" t="n">
-        <v>58043</v>
+        <v>58045</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6890,7 +6890,7 @@
         <v>131158214</v>
       </c>
       <c r="B54" t="n">
-        <v>58043</v>
+        <v>58045</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>

--- a/artfynd/A 52871-2025 artfynd.xlsx
+++ b/artfynd/A 52871-2025 artfynd.xlsx
@@ -6558,7 +6558,7 @@
         <v>131158283</v>
       </c>
       <c r="B51" t="n">
-        <v>58045</v>
+        <v>58046</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6672,7 +6672,7 @@
         <v>131158205</v>
       </c>
       <c r="B52" t="n">
-        <v>58045</v>
+        <v>58046</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6781,7 +6781,7 @@
         <v>131158127</v>
       </c>
       <c r="B53" t="n">
-        <v>58045</v>
+        <v>58046</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6890,7 +6890,7 @@
         <v>131158214</v>
       </c>
       <c r="B54" t="n">
-        <v>58045</v>
+        <v>58046</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>

--- a/artfynd/A 52871-2025 artfynd.xlsx
+++ b/artfynd/A 52871-2025 artfynd.xlsx
@@ -6558,7 +6558,7 @@
         <v>131158283</v>
       </c>
       <c r="B51" t="n">
-        <v>58046</v>
+        <v>58047</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6672,7 +6672,7 @@
         <v>131158205</v>
       </c>
       <c r="B52" t="n">
-        <v>58046</v>
+        <v>58047</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6781,7 +6781,7 @@
         <v>131158127</v>
       </c>
       <c r="B53" t="n">
-        <v>58046</v>
+        <v>58047</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6890,7 +6890,7 @@
         <v>131158214</v>
       </c>
       <c r="B54" t="n">
-        <v>58046</v>
+        <v>58047</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>

--- a/artfynd/A 52871-2025 artfynd.xlsx
+++ b/artfynd/A 52871-2025 artfynd.xlsx
@@ -6558,7 +6558,7 @@
         <v>131158283</v>
       </c>
       <c r="B51" t="n">
-        <v>58047</v>
+        <v>58050</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6672,7 +6672,7 @@
         <v>131158205</v>
       </c>
       <c r="B52" t="n">
-        <v>58047</v>
+        <v>58050</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6781,7 +6781,7 @@
         <v>131158127</v>
       </c>
       <c r="B53" t="n">
-        <v>58047</v>
+        <v>58050</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6890,7 +6890,7 @@
         <v>131158214</v>
       </c>
       <c r="B54" t="n">
-        <v>58047</v>
+        <v>58050</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>

--- a/artfynd/A 52871-2025 artfynd.xlsx
+++ b/artfynd/A 52871-2025 artfynd.xlsx
@@ -6558,7 +6558,7 @@
         <v>131158283</v>
       </c>
       <c r="B51" t="n">
-        <v>58050</v>
+        <v>58051</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6672,7 +6672,7 @@
         <v>131158205</v>
       </c>
       <c r="B52" t="n">
-        <v>58050</v>
+        <v>58051</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6781,7 +6781,7 @@
         <v>131158127</v>
       </c>
       <c r="B53" t="n">
-        <v>58050</v>
+        <v>58051</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6890,7 +6890,7 @@
         <v>131158214</v>
       </c>
       <c r="B54" t="n">
-        <v>58050</v>
+        <v>58051</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>

--- a/artfynd/A 52871-2025 artfynd.xlsx
+++ b/artfynd/A 52871-2025 artfynd.xlsx
@@ -6558,7 +6558,7 @@
         <v>131158283</v>
       </c>
       <c r="B51" t="n">
-        <v>58051</v>
+        <v>58057</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6672,7 +6672,7 @@
         <v>131158205</v>
       </c>
       <c r="B52" t="n">
-        <v>58051</v>
+        <v>58057</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6781,7 +6781,7 @@
         <v>131158127</v>
       </c>
       <c r="B53" t="n">
-        <v>58051</v>
+        <v>58057</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6890,7 +6890,7 @@
         <v>131158214</v>
       </c>
       <c r="B54" t="n">
-        <v>58051</v>
+        <v>58057</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>

--- a/artfynd/A 52871-2025 artfynd.xlsx
+++ b/artfynd/A 52871-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY54"/>
+  <dimension ref="A1:AY57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6994,6 +6994,343 @@
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>131714430</v>
+      </c>
+      <c r="B55" t="n">
+        <v>58057</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Hundviken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>525732</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6716237</v>
+      </c>
+      <c r="S55" t="n">
+        <v>5</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Aspeboda</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Talltita är uppenbarligen bofast i området. Varje helg observeras ett par som är del av meståg som drar igenom skogen i jakt på föda.</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Daniel Alexandersson</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Daniel Alexandersson</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>131714363</v>
+      </c>
+      <c r="B56" t="n">
+        <v>58057</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Hundviken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>525686</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6716226</v>
+      </c>
+      <c r="S56" t="n">
+        <v>5</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Aspeboda</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Daniel Alexandersson</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Daniel Alexandersson</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>131714401</v>
+      </c>
+      <c r="B57" t="n">
+        <v>58057</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Hundviken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>525613</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6716157</v>
+      </c>
+      <c r="S57" t="n">
+        <v>5</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Aspeboda</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Upptäckt först med app i samband med promenad längs vägen. Sedan observeras två individer.</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Daniel Alexandersson</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Daniel Alexandersson</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 52871-2025 artfynd.xlsx
+++ b/artfynd/A 52871-2025 artfynd.xlsx
@@ -6999,7 +6999,7 @@
         <v>131714430</v>
       </c>
       <c r="B55" t="n">
-        <v>58057</v>
+        <v>58058</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7113,7 +7113,7 @@
         <v>131714363</v>
       </c>
       <c r="B56" t="n">
-        <v>58057</v>
+        <v>58058</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7222,7 +7222,7 @@
         <v>131714401</v>
       </c>
       <c r="B57" t="n">
-        <v>58057</v>
+        <v>58058</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>

--- a/artfynd/A 52871-2025 artfynd.xlsx
+++ b/artfynd/A 52871-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY57"/>
+  <dimension ref="A1:AY58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6999,7 +6999,7 @@
         <v>131714430</v>
       </c>
       <c r="B55" t="n">
-        <v>58058</v>
+        <v>58061</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7113,7 +7113,7 @@
         <v>131714363</v>
       </c>
       <c r="B56" t="n">
-        <v>58058</v>
+        <v>58061</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7222,7 +7222,7 @@
         <v>131714401</v>
       </c>
       <c r="B57" t="n">
-        <v>58058</v>
+        <v>58061</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7330,6 +7330,127 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>131822536</v>
+      </c>
+      <c r="B58" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Hundviken, Hundviken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>525573</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6716073</v>
+      </c>
+      <c r="S58" t="n">
+        <v>5</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Aspeboda</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Milada Alexandersson</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Milada Alexandersson</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 52871-2025 artfynd.xlsx
+++ b/artfynd/A 52871-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY58"/>
+  <dimension ref="A1:AY59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7452,6 +7452,127 @@
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>131856463</v>
+      </c>
+      <c r="B59" t="n">
+        <v>58061</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Hundviken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>525687</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6716204</v>
+      </c>
+      <c r="S59" t="n">
+        <v>5</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Aspeboda</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Ser två stycken talltitor och identifierar med Merlin app</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Milada Alexandersson</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Milada Alexandersson</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 52871-2025 artfynd.xlsx
+++ b/artfynd/A 52871-2025 artfynd.xlsx
@@ -6999,7 +6999,7 @@
         <v>131714430</v>
       </c>
       <c r="B55" t="n">
-        <v>58061</v>
+        <v>58063</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7110,10 +7110,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131714363</v>
+        <v>131714401</v>
       </c>
       <c r="B56" t="n">
-        <v>58061</v>
+        <v>58063</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7140,7 +7140,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
@@ -7157,10 +7157,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>525686</v>
+        <v>525613</v>
       </c>
       <c r="R56" t="n">
-        <v>6716226</v>
+        <v>6716157</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -7187,12 +7187,17 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Upptäckt först med app i samband med promenad längs vägen. Sedan observeras två individer.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7219,10 +7224,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>131714401</v>
+        <v>131714363</v>
       </c>
       <c r="B57" t="n">
-        <v>58061</v>
+        <v>58063</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7249,7 +7254,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K57" t="inlineStr"/>
@@ -7266,10 +7271,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>525613</v>
+        <v>525686</v>
       </c>
       <c r="R57" t="n">
-        <v>6716157</v>
+        <v>6716226</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -7296,17 +7301,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Upptäckt först med app i samband med promenad längs vägen. Sedan observeras två individer.</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7336,7 +7336,7 @@
         <v>131822536</v>
       </c>
       <c r="B58" t="n">
-        <v>99038</v>
+        <v>99044</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7457,7 +7457,7 @@
         <v>131856463</v>
       </c>
       <c r="B59" t="n">
-        <v>58061</v>
+        <v>58063</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 52871-2025 artfynd.xlsx
+++ b/artfynd/A 52871-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY59"/>
+  <dimension ref="A1:AY62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7573,6 +7573,359 @@
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>131985054</v>
+      </c>
+      <c r="B60" t="n">
+        <v>99046</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Hundviken, Hundviken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>525629</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6716057</v>
+      </c>
+      <c r="S60" t="n">
+        <v>5</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Aspeboda</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Milada Alexandersson</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Milada Alexandersson</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>131985410</v>
+      </c>
+      <c r="B61" t="n">
+        <v>99046</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Hundviken, Hundviken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>525611</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6716076</v>
+      </c>
+      <c r="S61" t="n">
+        <v>5</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Aspeboda</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Milada Alexandersson</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Milada Alexandersson</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>131985295</v>
+      </c>
+      <c r="B62" t="n">
+        <v>99046</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Hundviken, Hundviken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>525591</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6716100</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Aspeboda</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Milada Alexandersson</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Milada Alexandersson</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 52871-2025 artfynd.xlsx
+++ b/artfynd/A 52871-2025 artfynd.xlsx
@@ -6999,7 +6999,7 @@
         <v>131714430</v>
       </c>
       <c r="B55" t="n">
-        <v>58063</v>
+        <v>58066</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7110,10 +7110,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131714401</v>
+        <v>131714363</v>
       </c>
       <c r="B56" t="n">
-        <v>58063</v>
+        <v>58066</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7140,7 +7140,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
@@ -7157,10 +7157,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>525613</v>
+        <v>525686</v>
       </c>
       <c r="R56" t="n">
-        <v>6716157</v>
+        <v>6716226</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -7187,17 +7187,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Upptäckt först med app i samband med promenad längs vägen. Sedan observeras två individer.</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7224,10 +7219,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>131714363</v>
+        <v>131714401</v>
       </c>
       <c r="B57" t="n">
-        <v>58063</v>
+        <v>58066</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7254,7 +7249,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K57" t="inlineStr"/>
@@ -7271,10 +7266,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>525686</v>
+        <v>525613</v>
       </c>
       <c r="R57" t="n">
-        <v>6716226</v>
+        <v>6716157</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -7301,12 +7296,17 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Upptäckt först med app i samband med promenad längs vägen. Sedan observeras två individer.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7336,7 +7336,7 @@
         <v>131822536</v>
       </c>
       <c r="B58" t="n">
-        <v>99044</v>
+        <v>99047</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7457,7 +7457,7 @@
         <v>131856463</v>
       </c>
       <c r="B59" t="n">
-        <v>58063</v>
+        <v>58066</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7578,7 +7578,7 @@
         <v>131985054</v>
       </c>
       <c r="B60" t="n">
-        <v>99046</v>
+        <v>99047</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7699,7 +7699,7 @@
         <v>131985410</v>
       </c>
       <c r="B61" t="n">
-        <v>99046</v>
+        <v>99047</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7810,7 +7810,7 @@
         <v>131985295</v>
       </c>
       <c r="B62" t="n">
-        <v>99046</v>
+        <v>99047</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>

--- a/artfynd/A 52871-2025 artfynd.xlsx
+++ b/artfynd/A 52871-2025 artfynd.xlsx
@@ -6999,7 +6999,7 @@
         <v>131714430</v>
       </c>
       <c r="B55" t="n">
-        <v>58066</v>
+        <v>58071</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7113,7 +7113,7 @@
         <v>131714363</v>
       </c>
       <c r="B56" t="n">
-        <v>58066</v>
+        <v>58071</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7222,7 +7222,7 @@
         <v>131714401</v>
       </c>
       <c r="B57" t="n">
-        <v>58066</v>
+        <v>58071</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7336,7 +7336,7 @@
         <v>131822536</v>
       </c>
       <c r="B58" t="n">
-        <v>99047</v>
+        <v>99052</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7457,7 +7457,7 @@
         <v>131856463</v>
       </c>
       <c r="B59" t="n">
-        <v>58066</v>
+        <v>58071</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7578,7 +7578,7 @@
         <v>131985054</v>
       </c>
       <c r="B60" t="n">
-        <v>99047</v>
+        <v>99052</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7699,7 +7699,7 @@
         <v>131985410</v>
       </c>
       <c r="B61" t="n">
-        <v>99047</v>
+        <v>99052</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7810,7 +7810,7 @@
         <v>131985295</v>
       </c>
       <c r="B62" t="n">
-        <v>99047</v>
+        <v>99052</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>

--- a/artfynd/A 52871-2025 artfynd.xlsx
+++ b/artfynd/A 52871-2025 artfynd.xlsx
@@ -6999,7 +6999,7 @@
         <v>131714430</v>
       </c>
       <c r="B55" t="n">
-        <v>58107</v>
+        <v>58109</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7113,7 +7113,7 @@
         <v>131714363</v>
       </c>
       <c r="B56" t="n">
-        <v>58107</v>
+        <v>58109</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7222,7 +7222,7 @@
         <v>131714401</v>
       </c>
       <c r="B57" t="n">
-        <v>58107</v>
+        <v>58109</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7336,7 +7336,7 @@
         <v>131822536</v>
       </c>
       <c r="B58" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7457,7 +7457,7 @@
         <v>131856463</v>
       </c>
       <c r="B59" t="n">
-        <v>58107</v>
+        <v>58109</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7578,7 +7578,7 @@
         <v>131985054</v>
       </c>
       <c r="B60" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7699,7 +7699,7 @@
         <v>131985410</v>
       </c>
       <c r="B61" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7810,7 +7810,7 @@
         <v>131985295</v>
       </c>
       <c r="B62" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>

--- a/artfynd/A 52871-2025 artfynd.xlsx
+++ b/artfynd/A 52871-2025 artfynd.xlsx
@@ -7578,7 +7578,7 @@
         <v>131985054</v>
       </c>
       <c r="B60" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7699,7 +7699,7 @@
         <v>131985410</v>
       </c>
       <c r="B61" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7810,7 +7810,7 @@
         <v>131985295</v>
       </c>
       <c r="B62" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>

--- a/artfynd/A 52871-2025 artfynd.xlsx
+++ b/artfynd/A 52871-2025 artfynd.xlsx
@@ -7578,7 +7578,7 @@
         <v>131985054</v>
       </c>
       <c r="B60" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7699,7 +7699,7 @@
         <v>131985410</v>
       </c>
       <c r="B61" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7810,7 +7810,7 @@
         <v>131985295</v>
       </c>
       <c r="B62" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>

--- a/artfynd/A 52871-2025 artfynd.xlsx
+++ b/artfynd/A 52871-2025 artfynd.xlsx
@@ -7578,7 +7578,7 @@
         <v>131985054</v>
       </c>
       <c r="B60" t="n">
-        <v>99116</v>
+        <v>99118</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7699,7 +7699,7 @@
         <v>131985410</v>
       </c>
       <c r="B61" t="n">
-        <v>99116</v>
+        <v>99118</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7810,7 +7810,7 @@
         <v>131985295</v>
       </c>
       <c r="B62" t="n">
-        <v>99116</v>
+        <v>99118</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>

--- a/artfynd/A 52871-2025 artfynd.xlsx
+++ b/artfynd/A 52871-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY62"/>
+  <dimension ref="A1:AY70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,52 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127315588</v>
+        <v>129339939</v>
       </c>
       <c r="B2" t="n">
-        <v>98469</v>
+        <v>93235</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>5966</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -729,13 +714,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>525666</v>
+        <v>525799</v>
       </c>
       <c r="R2" t="n">
-        <v>6716159</v>
+        <v>6716284</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,22 +744,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Med tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -801,67 +791,55 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127315514</v>
+        <v>130158729</v>
       </c>
       <c r="B3" t="n">
-        <v>98469</v>
+        <v>79351</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6434</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hundviken, Hundviken, Dlr</t>
+          <t>Hundviken, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>525676</v>
+        <v>525746</v>
       </c>
       <c r="R3" t="n">
-        <v>6716168</v>
+        <v>6716214</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -885,22 +863,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>12:03</t>
+          <t>2025-12-07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>12:03</t>
+          <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Flertalet observeras på tallar som nyligen blåst omkull. Möjliggör inspektion längs hela trädens längd. Extra intressant fynd då arten indikerar äldre, skyddsvärd skog söder om naturliga norrlandsgränsen.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,85 +882,70 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Milada Alexandersson</t>
+          <t>Daniel Alexandersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Milada Alexandersson</t>
+          <t>Daniel Alexandersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127316295</v>
+        <v>130125217</v>
       </c>
       <c r="B4" t="n">
-        <v>98469</v>
+        <v>78730</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6437</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hundviken, Hundviken, Dlr</t>
+          <t>Hundviken, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>525743</v>
+        <v>525602</v>
       </c>
       <c r="R4" t="n">
-        <v>6716220</v>
+        <v>6716070</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1011,22 +969,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-12-14</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-12-14</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>13:37</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På död högstubbe av tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1035,6 +998,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1053,62 +1017,53 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127314167</v>
+        <v>129979188</v>
       </c>
       <c r="B5" t="n">
-        <v>98469</v>
+        <v>57950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hundviken, Hundviken, Dlr</t>
+          <t>Stående död tall, "smedjor", Stående död tall, "smedjor", Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>525686</v>
+        <v>525724</v>
       </c>
       <c r="R5" t="n">
-        <v>6716155</v>
+        <v>6716195</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1132,22 +1087,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1174,32 +1129,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127315222</v>
+        <v>129339792</v>
       </c>
       <c r="B6" t="n">
-        <v>98469</v>
+        <v>57945</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100110</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>J.F. Gmelin, 1788</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1207,19 +1162,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1228,13 +1173,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>525682</v>
+        <v>525822</v>
       </c>
       <c r="R6" t="n">
-        <v>6716184</v>
+        <v>6716256</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1258,22 +1203,27 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Hördes österut från denna plats</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1300,67 +1250,53 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127315716</v>
+        <v>129979221</v>
       </c>
       <c r="B7" t="n">
-        <v>98469</v>
+        <v>57945</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100110</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>J.F. Gmelin, 1788</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hundviken, Hundviken, Dlr</t>
+          <t>Stående död tall, Stående död tall, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>525670</v>
+        <v>525782</v>
       </c>
       <c r="R7" t="n">
-        <v>6716189</v>
+        <v>6716244</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1384,22 +1320,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1426,42 +1362,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127316344</v>
+        <v>129731617</v>
       </c>
       <c r="B8" t="n">
-        <v>98469</v>
+        <v>57811</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100137</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Slaguggla</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Strix uralensis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Pallas, 1771</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>rastande</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1471,17 +1413,17 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Hundviken, Hundviken, Dlr</t>
+          <t>Stråtenbo 62, Stråtenbo, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>525736</v>
+        <v>525535</v>
       </c>
       <c r="R8" t="n">
-        <v>6716217</v>
+        <v>6716136</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1505,22 +1447,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>12:47</t>
+          <t>2025-05-15</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>12:47</t>
+          <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Vuxen slaguggla på besök från närliggande boplats</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1535,44 +1472,48 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Milada Alexandersson</t>
+          <t>Kenneth Smith</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Milada Alexandersson</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
+          <t>Kenneth Smith</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Privat inventering</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127316136</v>
+        <v>129721082</v>
       </c>
       <c r="B9" t="n">
-        <v>98469</v>
+        <v>57794</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>102621</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1580,34 +1521,27 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hundviken, Hundviken, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>525712</v>
+        <v>525783</v>
       </c>
       <c r="R9" t="n">
-        <v>6716193</v>
+        <v>6716330</v>
       </c>
       <c r="S9" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1631,22 +1565,27 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Sitter på toppen av en gran och bevakar.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1673,67 +1612,53 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127316228</v>
+        <v>129747025</v>
       </c>
       <c r="B10" t="n">
-        <v>98469</v>
+        <v>57794</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>102621</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Hundviken, Hundviken, Dlr</t>
+          <t>Stående död tall, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>525740</v>
+        <v>525786</v>
       </c>
       <c r="R10" t="n">
-        <v>6716244</v>
+        <v>6716281</v>
       </c>
       <c r="S10" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1757,22 +1682,27 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Sitter på toppen av en gran och bevakar.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1799,67 +1729,57 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127314992</v>
+        <v>129938268</v>
       </c>
       <c r="B11" t="n">
-        <v>98469</v>
+        <v>58112</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>103020</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Hundviken, Hundviken, Dlr</t>
+          <t>Stående död tall, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>525694</v>
+        <v>525775</v>
       </c>
       <c r="R11" t="n">
-        <v>6716178</v>
+        <v>6716218</v>
       </c>
       <c r="S11" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1883,22 +1803,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>11:42</t>
+          <t>2025-04-11</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>11:42</t>
+          <t>2025-04-11</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1925,67 +1835,53 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127316105</v>
+        <v>129979175</v>
       </c>
       <c r="B12" t="n">
-        <v>98469</v>
+        <v>58112</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>103020</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Hundviken, Hundviken, Dlr</t>
+          <t>Stående död tall, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>525712</v>
+        <v>525766</v>
       </c>
       <c r="R12" t="n">
-        <v>6716192</v>
+        <v>6716251</v>
       </c>
       <c r="S12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2009,22 +1905,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>12:29</t>
+          <t>2025-04-11</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>12:29</t>
+          <t>2025-04-11</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2051,32 +1937,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127316409</v>
+        <v>131158127</v>
       </c>
       <c r="B13" t="n">
-        <v>98469</v>
+        <v>58114</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -2084,34 +1970,27 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Hundviken, Hundviken, Dlr</t>
+          <t>Hundviken, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>525735</v>
+        <v>525695</v>
       </c>
       <c r="R13" t="n">
-        <v>6716213</v>
+        <v>6716177</v>
       </c>
       <c r="S13" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2135,22 +2014,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>12:47</t>
+          <t>2026-01-11</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>12:47</t>
+          <t>2026-01-11</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2165,44 +2034,44 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Milada Alexandersson</t>
+          <t>Daniel Alexandersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Milada Alexandersson</t>
+          <t>Daniel Alexandersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127315619</v>
+        <v>131158205</v>
       </c>
       <c r="B14" t="n">
-        <v>98469</v>
+        <v>58114</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2210,34 +2079,27 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Hundviken, Hundviken, Dlr</t>
+          <t>Hundviken, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>525656</v>
+        <v>525731</v>
       </c>
       <c r="R14" t="n">
-        <v>6716166</v>
+        <v>6716197</v>
       </c>
       <c r="S14" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2261,22 +2123,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>12:10</t>
+          <t>2026-02-08</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>12:10</t>
+          <t>2026-02-08</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2291,79 +2143,72 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Milada Alexandersson</t>
+          <t>Daniel Alexandersson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Milada Alexandersson</t>
+          <t>Daniel Alexandersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127315460</v>
+        <v>131158214</v>
       </c>
       <c r="B15" t="n">
-        <v>98469</v>
+        <v>58114</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Hundviken, Hundviken, Dlr</t>
+          <t>Hundviken, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>525688</v>
+        <v>525566</v>
       </c>
       <c r="R15" t="n">
-        <v>6716179</v>
+        <v>6716104</v>
       </c>
       <c r="S15" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2387,22 +2232,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>12:00</t>
+          <t>2026-01-25</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>12:00</t>
+          <t>2026-01-25</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2417,44 +2252,44 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Milada Alexandersson</t>
+          <t>Daniel Alexandersson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Milada Alexandersson</t>
+          <t>Daniel Alexandersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127315125</v>
+        <v>131158283</v>
       </c>
       <c r="B16" t="n">
-        <v>98469</v>
+        <v>58114</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2462,34 +2297,27 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Hundviken, Hundviken, Dlr</t>
+          <t>Hundviken, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>525684</v>
+        <v>525550</v>
       </c>
       <c r="R16" t="n">
-        <v>6716162</v>
+        <v>6716117</v>
       </c>
       <c r="S16" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2513,22 +2341,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>11:42</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>11:42</t>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Hört fågeln och registrerat med app.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2543,44 +2366,44 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Milada Alexandersson</t>
+          <t>Daniel Alexandersson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Milada Alexandersson</t>
+          <t>Daniel Alexandersson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127316162</v>
+        <v>131158288</v>
       </c>
       <c r="B17" t="n">
-        <v>98469</v>
+        <v>58114</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2588,34 +2411,27 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Hundviken, Hundviken, Dlr</t>
+          <t>Hundviken, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>525752</v>
+        <v>525513</v>
       </c>
       <c r="R17" t="n">
-        <v>6716206</v>
+        <v>6716073</v>
       </c>
       <c r="S17" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2639,22 +2455,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>12:36</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>12:36</t>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Hört och registrerat med app</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2669,79 +2480,72 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Milada Alexandersson</t>
+          <t>Daniel Alexandersson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Milada Alexandersson</t>
+          <t>Daniel Alexandersson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127313556</v>
+        <v>131714363</v>
       </c>
       <c r="B18" t="n">
-        <v>98469</v>
+        <v>58136</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Hundviken, Hundviken, Dlr</t>
+          <t>Hundviken, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>525685</v>
+        <v>525686</v>
       </c>
       <c r="R18" t="n">
-        <v>6716175</v>
+        <v>6716226</v>
       </c>
       <c r="S18" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2765,22 +2569,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>11:08</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>11:08</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2795,44 +2589,44 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Milada Alexandersson</t>
+          <t>Daniel Alexandersson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Milada Alexandersson</t>
+          <t>Daniel Alexandersson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127314541</v>
+        <v>131714401</v>
       </c>
       <c r="B19" t="n">
-        <v>98469</v>
+        <v>58136</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2840,34 +2634,27 @@
           <t>2</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Hundviken, Hundviken, Dlr</t>
+          <t>Hundviken, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>525690</v>
+        <v>525613</v>
       </c>
       <c r="R19" t="n">
-        <v>6716175</v>
+        <v>6716157</v>
       </c>
       <c r="S19" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2891,22 +2678,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>11:28</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>11:28</t>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Upptäckt först med app i samband med promenad längs vägen. Sedan observeras två individer.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2921,69 +2703,72 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Milada Alexandersson</t>
+          <t>Daniel Alexandersson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Milada Alexandersson</t>
+          <t>Daniel Alexandersson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127351108</v>
+        <v>131714430</v>
       </c>
       <c r="B20" t="n">
-        <v>98470</v>
+        <v>58136</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Hundviken, Hundviken, Dlr</t>
+          <t>Hundviken, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>525674</v>
+        <v>525732</v>
       </c>
       <c r="R20" t="n">
-        <v>6716190</v>
+        <v>6716237</v>
       </c>
       <c r="S20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3007,27 +2792,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-08-09</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>18:56</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-08-09</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>18:56</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>1 stjälke</t>
+          <t>Talltita är uppenbarligen bofast i området. Varje helg observeras ett par som är del av meståg som drar igenom skogen i jakt på föda.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3042,69 +2817,69 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Milada Alexandersson</t>
+          <t>Daniel Alexandersson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Milada Alexandersson</t>
+          <t>Daniel Alexandersson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127351427</v>
+        <v>131856463</v>
       </c>
       <c r="B21" t="n">
-        <v>98470</v>
+        <v>58136</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Hundviken, Hundviken, Dlr</t>
+          <t>Hundviken, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>525690</v>
+        <v>525687</v>
       </c>
       <c r="R21" t="n">
-        <v>6716183</v>
+        <v>6716204</v>
       </c>
       <c r="S21" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3128,27 +2903,27 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-08-09</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-08-09</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>1 stjälke</t>
+          <t>Ser två stycken talltitor och identifierar med Merlin app</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3175,42 +2950,38 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127351240</v>
+        <v>129339605</v>
       </c>
       <c r="B22" t="n">
-        <v>98470</v>
+        <v>8455</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3219,13 +2990,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>525680</v>
+        <v>525780</v>
       </c>
       <c r="R22" t="n">
-        <v>6716185</v>
+        <v>6716226</v>
       </c>
       <c r="S22" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3249,22 +3020,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-08-09</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-08-09</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3291,42 +3062,38 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127351678</v>
+        <v>129340891</v>
       </c>
       <c r="B23" t="n">
-        <v>98470</v>
+        <v>8455</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3335,13 +3102,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>525682</v>
+        <v>525685</v>
       </c>
       <c r="R23" t="n">
-        <v>6716183</v>
+        <v>6716122</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3365,22 +3132,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-08-09</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>19:23</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-08-09</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>19:23</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3407,57 +3174,61 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127351377</v>
+        <v>130044230</v>
       </c>
       <c r="B24" t="n">
-        <v>98470</v>
+        <v>58817</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>208249</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Hundviken, Hundviken, Dlr</t>
+          <t>Intill väg, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>525680</v>
+        <v>525653</v>
       </c>
       <c r="R24" t="n">
-        <v>6716172</v>
+        <v>6716143</v>
       </c>
       <c r="S24" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3484,24 +3255,14 @@
           <t>2025-08-09</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>19:07</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-08-09</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>19:07</t>
-        </is>
-      </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>1 stjälke</t>
+          <t>Stor för att vara vanlig groda. Närmast paddstorlek.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3510,75 +3271,76 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Milada Alexandersson</t>
+          <t>Daniel Alexandersson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Milada Alexandersson</t>
+          <t>Daniel Alexandersson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127351465</v>
+        <v>129727312</v>
       </c>
       <c r="B25" t="n">
-        <v>98470</v>
+        <v>58815</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>208250</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Hundviken, Hundviken, Dlr</t>
+          <t>Åkergroda, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>525676</v>
+        <v>525655</v>
       </c>
       <c r="R25" t="n">
-        <v>6716177</v>
+        <v>6716145</v>
       </c>
       <c r="S25" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3602,27 +3364,17 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-08-09</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>19:13</t>
+          <t>2025-08-17</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-08-09</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>19:13</t>
+          <t>2025-08-17</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>2 stjälkar</t>
+          <t>Fotad och eftergranskad av grodexpert</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3631,6 +3383,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3649,57 +3402,61 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127350965</v>
+        <v>130022082</v>
       </c>
       <c r="B26" t="n">
-        <v>98470</v>
+        <v>56884</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>208255</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Zootoca vivipara</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Jacquin, 1787)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Hundviken, Hundviken, Dlr</t>
+          <t>Intill väg, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>525685</v>
+        <v>525632</v>
       </c>
       <c r="R26" t="n">
-        <v>6716229</v>
+        <v>6716152</v>
       </c>
       <c r="S26" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3723,27 +3480,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-08-09</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>18:49</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-08-09</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>18:49</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>1 stjälke</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3752,55 +3494,71 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Milada Alexandersson</t>
+          <t>Daniel Alexandersson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Milada Alexandersson</t>
+          <t>Daniel Alexandersson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129339939</v>
+        <v>127313556</v>
       </c>
       <c r="B27" t="n">
-        <v>92913</v>
+        <v>99118</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5966</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3809,13 +3567,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>525799</v>
+        <v>525685</v>
       </c>
       <c r="R27" t="n">
-        <v>6716284</v>
+        <v>6716175</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3839,27 +3597,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:34</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Med tall</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3886,10 +3639,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129340627</v>
+        <v>127314167</v>
       </c>
       <c r="B28" t="n">
-        <v>98774</v>
+        <v>99118</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3916,17 +3669,17 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3935,13 +3688,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>525709</v>
+        <v>525686</v>
       </c>
       <c r="R28" t="n">
-        <v>6716198</v>
+        <v>6716155</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3965,22 +3718,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4007,38 +3760,52 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129339605</v>
+        <v>127314541</v>
       </c>
       <c r="B29" t="n">
-        <v>8450</v>
+        <v>99118</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -4047,13 +3814,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>525780</v>
+        <v>525690</v>
       </c>
       <c r="R29" t="n">
-        <v>6716226</v>
+        <v>6716175</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4077,22 +3844,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4119,10 +3886,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129338657</v>
+        <v>127314992</v>
       </c>
       <c r="B30" t="n">
-        <v>98774</v>
+        <v>99118</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4149,17 +3916,22 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -4168,13 +3940,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>525677</v>
+        <v>525694</v>
       </c>
       <c r="R30" t="n">
-        <v>6716163</v>
+        <v>6716178</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4198,27 +3970,22 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:38</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>1 överblommad</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4245,10 +4012,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129339191</v>
+        <v>127315125</v>
       </c>
       <c r="B31" t="n">
-        <v>98774</v>
+        <v>99118</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4275,12 +4042,22 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4289,13 +4066,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>525746</v>
+        <v>525684</v>
       </c>
       <c r="R31" t="n">
-        <v>6716215</v>
+        <v>6716162</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4319,22 +4096,22 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4361,10 +4138,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129339551</v>
+        <v>127315222</v>
       </c>
       <c r="B32" t="n">
-        <v>98774</v>
+        <v>99118</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4391,17 +4168,22 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4410,13 +4192,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>525769</v>
+        <v>525682</v>
       </c>
       <c r="R32" t="n">
-        <v>6716224</v>
+        <v>6716184</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4440,22 +4222,22 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4482,10 +4264,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129338511</v>
+        <v>127315460</v>
       </c>
       <c r="B33" t="n">
-        <v>98774</v>
+        <v>99118</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4512,12 +4294,22 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4526,13 +4318,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>525680</v>
+        <v>525688</v>
       </c>
       <c r="R33" t="n">
-        <v>6716143</v>
+        <v>6716179</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4556,27 +4348,22 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:31</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ca 20 bladrosetter 1 överblommade</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4603,10 +4390,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129338899</v>
+        <v>127315514</v>
       </c>
       <c r="B34" t="n">
-        <v>98774</v>
+        <v>99118</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4633,17 +4420,22 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4652,13 +4444,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>525712</v>
+        <v>525676</v>
       </c>
       <c r="R34" t="n">
-        <v>6716201</v>
+        <v>6716168</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4682,22 +4474,22 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4724,10 +4516,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129339499</v>
+        <v>127315588</v>
       </c>
       <c r="B35" t="n">
-        <v>98774</v>
+        <v>99118</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4754,17 +4546,22 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4773,13 +4570,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>525771</v>
+        <v>525666</v>
       </c>
       <c r="R35" t="n">
-        <v>6716245</v>
+        <v>6716159</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4803,27 +4600,22 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:09</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Spridda över ca 0,5 m2</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4850,10 +4642,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129340696</v>
+        <v>127315619</v>
       </c>
       <c r="B36" t="n">
-        <v>98774</v>
+        <v>99118</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4880,12 +4672,22 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4894,13 +4696,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>525672</v>
+        <v>525656</v>
       </c>
       <c r="R36" t="n">
-        <v>6716190</v>
+        <v>6716166</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4924,27 +4726,22 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:59</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>På stenblock! 2 överblommade</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4971,10 +4768,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129338834</v>
+        <v>127315716</v>
       </c>
       <c r="B37" t="n">
-        <v>98774</v>
+        <v>99118</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5001,12 +4798,22 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -5015,13 +4822,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>525715</v>
+        <v>525670</v>
       </c>
       <c r="R37" t="n">
-        <v>6716181</v>
+        <v>6716189</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5045,22 +4852,22 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5087,10 +4894,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129338590</v>
+        <v>127316105</v>
       </c>
       <c r="B38" t="n">
-        <v>98774</v>
+        <v>99118</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5117,7 +4924,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -5125,16 +4937,21 @@
           <t>överblommad</t>
         </is>
       </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Hundviken, Hundviken, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>525673</v>
+        <v>525712</v>
       </c>
       <c r="R38" t="n">
-        <v>6716152</v>
+        <v>6716192</v>
       </c>
       <c r="S38" t="n">
         <v>1</v>
@@ -5161,22 +4978,22 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5203,32 +5020,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129727312</v>
+        <v>127316136</v>
       </c>
       <c r="B39" t="n">
-        <v>58600</v>
+        <v>99118</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>208250</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -5236,24 +5053,34 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Åkergroda, Dlr</t>
+          <t>Hundviken, Hundviken, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>525655</v>
+        <v>525712</v>
       </c>
       <c r="R39" t="n">
-        <v>6716145</v>
+        <v>6716193</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5277,17 +5104,22 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-08-17</t>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-08-17</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Fotad och eftergranskad av grodexpert</t>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5296,7 +5128,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -5315,53 +5146,67 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129747025</v>
+        <v>127316162</v>
       </c>
       <c r="B40" t="n">
-        <v>57581</v>
+        <v>99118</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>102621</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Stående död tall, Dlr</t>
+          <t>Hundviken, Hundviken, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>525786</v>
+        <v>525752</v>
       </c>
       <c r="R40" t="n">
-        <v>6716281</v>
+        <v>6716206</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5385,27 +5230,22 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:22</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Sitter på toppen av en gran och bevakar.</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5432,53 +5272,67 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129979175</v>
+        <v>127316228</v>
       </c>
       <c r="B41" t="n">
-        <v>57983</v>
+        <v>99118</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103020</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Stående död tall, Dlr</t>
+          <t>Hundviken, Hundviken, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>525766</v>
+        <v>525740</v>
       </c>
       <c r="R41" t="n">
-        <v>6716251</v>
+        <v>6716244</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5502,12 +5356,22 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-04-11</t>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-04-11</t>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5534,53 +5398,67 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129979188</v>
+        <v>127316295</v>
       </c>
       <c r="B42" t="n">
-        <v>57823</v>
+        <v>99118</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Stående död tall, "smedjor", Stående död tall, "smedjor", Dlr</t>
+          <t>Hundviken, Hundviken, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>525724</v>
+        <v>525743</v>
       </c>
       <c r="R42" t="n">
-        <v>6716195</v>
+        <v>6716220</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5604,22 +5482,22 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5646,50 +5524,59 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129979221</v>
+        <v>127316344</v>
       </c>
       <c r="B43" t="n">
-        <v>57818</v>
+        <v>99118</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100110</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Stående död tall, Stående död tall, Dlr</t>
+          <t>Hundviken, Hundviken, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>525782</v>
+        <v>525736</v>
       </c>
       <c r="R43" t="n">
-        <v>6716244</v>
+        <v>6716217</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5716,22 +5603,22 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5758,32 +5645,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130022082</v>
+        <v>127316409</v>
       </c>
       <c r="B44" t="n">
-        <v>56758</v>
+        <v>99118</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>208255</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Zootoca vivipara</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Jacquin, 1787)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -5793,26 +5680,32 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Intill väg, Dlr</t>
+          <t>Hundviken, Hundviken, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>525632</v>
+        <v>525735</v>
       </c>
       <c r="R44" t="n">
-        <v>6716152</v>
+        <v>6716213</v>
       </c>
       <c r="S44" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5836,12 +5729,22 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5850,29 +5753,28 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Daniel Alexandersson</t>
+          <t>Milada Alexandersson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Daniel Alexandersson</t>
+          <t>Milada Alexandersson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130016904</v>
+        <v>127350965</v>
       </c>
       <c r="B45" t="n">
-        <v>98920</v>
+        <v>99118</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5899,7 +5801,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -5909,17 +5811,17 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Hundviken, Dlr</t>
+          <t>Hundviken, Hundviken, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>525602</v>
+        <v>525685</v>
       </c>
       <c r="R45" t="n">
-        <v>6716070</v>
+        <v>6716229</v>
       </c>
       <c r="S45" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5943,22 +5845,27 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-12-07</t>
+          <t>2025-08-09</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>18:49</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-12-07</t>
+          <t>2025-08-09</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>18:49</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>1 stjälke</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5985,68 +5892,57 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129731617</v>
+        <v>127351108</v>
       </c>
       <c r="B46" t="n">
-        <v>57684</v>
+        <v>99118</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100137</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Slaguggla</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Strix uralensis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Pallas, 1771</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>rastande</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Stråtenbo 62, Stråtenbo, Dlr</t>
+          <t>Hundviken, Hundviken, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>525535</v>
+        <v>525674</v>
       </c>
       <c r="R46" t="n">
-        <v>6716136</v>
+        <v>6716190</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6070,17 +5966,27 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-05-15</t>
+          <t>2025-08-09</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>18:56</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-05-15</t>
+          <t>2025-08-09</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>18:56</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Vuxen slaguggla på besök från närliggande boplats</t>
+          <t>1 stjälke</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6095,77 +6001,69 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Kenneth Smith</t>
+          <t>Milada Alexandersson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Kenneth Smith</t>
-        </is>
-      </c>
-      <c r="AY46" t="inlineStr">
-        <is>
-          <t>Privat inventering</t>
-        </is>
-      </c>
+          <t>Milada Alexandersson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130044230</v>
+        <v>127351240</v>
       </c>
       <c r="B47" t="n">
-        <v>58688</v>
+        <v>99118</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>208249</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Intill väg, Dlr</t>
+          <t>Hundviken, Hundviken, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>525653</v>
+        <v>525680</v>
       </c>
       <c r="R47" t="n">
-        <v>6716143</v>
+        <v>6716185</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6192,14 +6090,19 @@
           <t>2025-08-09</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>19:03</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-08-09</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Stor för att vara vanlig groda. Närmast paddstorlek.</t>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6208,70 +6111,75 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Daniel Alexandersson</t>
+          <t>Milada Alexandersson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Daniel Alexandersson</t>
+          <t>Milada Alexandersson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130125217</v>
+        <v>127351377</v>
       </c>
       <c r="B48" t="n">
-        <v>78612</v>
+        <v>99118</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6437</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Hundviken, Dlr</t>
+          <t>Hundviken, Hundviken, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>525602</v>
+        <v>525680</v>
       </c>
       <c r="R48" t="n">
-        <v>6716070</v>
+        <v>6716172</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6295,27 +6203,27 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-12-14</t>
+          <t>2025-08-09</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>19:07</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-12-14</t>
+          <t>2025-08-09</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>19:07</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>På död högstubbe av tall</t>
+          <t>1 stjälke</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6324,7 +6232,6 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -6343,32 +6250,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130158729</v>
+        <v>127351427</v>
       </c>
       <c r="B49" t="n">
-        <v>79233</v>
+        <v>99118</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6434</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -6376,22 +6283,24 @@
           <t>10</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Hundviken, Dlr</t>
+          <t>Hundviken, Hundviken, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>525746</v>
+        <v>525690</v>
       </c>
       <c r="R49" t="n">
-        <v>6716214</v>
+        <v>6716183</v>
       </c>
       <c r="S49" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6415,17 +6324,27 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-12-07</t>
+          <t>2025-08-09</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>19:10</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-12-07</t>
+          <t>2025-08-09</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>19:10</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Flertalet observeras på tallar som nyligen blåst omkull. Möjliggör inspektion längs hela trädens längd. Extra intressant fynd då arten indikerar äldre, skyddsvärd skog söder om naturliga norrlandsgränsen.</t>
+          <t>1 stjälke</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6434,71 +6353,75 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Daniel Alexandersson</t>
+          <t>Milada Alexandersson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Daniel Alexandersson</t>
+          <t>Milada Alexandersson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130044041</v>
+        <v>127351465</v>
       </c>
       <c r="B50" t="n">
-        <v>97828</v>
+        <v>99118</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Hundviken, Dlr</t>
+          <t>Hundviken, Hundviken, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>525776</v>
+        <v>525676</v>
       </c>
       <c r="R50" t="n">
-        <v>6716252</v>
+        <v>6716177</v>
       </c>
       <c r="S50" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6522,12 +6445,27 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2025-08-09</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>19:13</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2025-08-09</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>19:13</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>2 stjälkar</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6536,76 +6474,72 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Daniel Alexandersson</t>
+          <t>Milada Alexandersson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Daniel Alexandersson</t>
+          <t>Milada Alexandersson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131158283</v>
+        <v>127351678</v>
       </c>
       <c r="B51" t="n">
-        <v>58057</v>
+        <v>99118</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Hundviken, Dlr</t>
+          <t>Hundviken, Hundviken, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>525550</v>
+        <v>525682</v>
       </c>
       <c r="R51" t="n">
-        <v>6716117</v>
+        <v>6716183</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6632,17 +6566,22 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2025-08-09</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>19:23</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Hört fågeln och registrerat med app.</t>
+          <t>2025-08-09</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>19:23</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6657,72 +6596,69 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Daniel Alexandersson</t>
+          <t>Milada Alexandersson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Daniel Alexandersson</t>
+          <t>Milada Alexandersson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131158205</v>
+        <v>129338511</v>
       </c>
       <c r="B52" t="n">
-        <v>58057</v>
+        <v>99118</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Hundviken, Dlr</t>
+          <t>Hundviken, Hundviken, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>525731</v>
+        <v>525680</v>
       </c>
       <c r="R52" t="n">
-        <v>6716197</v>
+        <v>6716143</v>
       </c>
       <c r="S52" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6746,12 +6682,27 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>10:31</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Ca 20 bladrosetter 1 överblommade</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6766,44 +6717,44 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Daniel Alexandersson</t>
+          <t>Milada Alexandersson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Daniel Alexandersson</t>
+          <t>Milada Alexandersson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131158127</v>
+        <v>129338590</v>
       </c>
       <c r="B53" t="n">
-        <v>58057</v>
+        <v>99118</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -6811,27 +6762,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Hundviken, Dlr</t>
+          <t>Hundviken, Hundviken, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>525695</v>
+        <v>525673</v>
       </c>
       <c r="R53" t="n">
-        <v>6716177</v>
+        <v>6716152</v>
       </c>
       <c r="S53" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6855,12 +6803,22 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2026-01-11</t>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-01-11</t>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6875,72 +6833,74 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Daniel Alexandersson</t>
+          <t>Milada Alexandersson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Daniel Alexandersson</t>
+          <t>Milada Alexandersson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131158214</v>
+        <v>129338657</v>
       </c>
       <c r="B54" t="n">
-        <v>58057</v>
+        <v>99118</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Hundviken, Dlr</t>
+          <t>Hundviken, Hundviken, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>525566</v>
+        <v>525677</v>
       </c>
       <c r="R54" t="n">
-        <v>6716104</v>
+        <v>6716163</v>
       </c>
       <c r="S54" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6964,12 +6924,27 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2026-01-25</t>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-01-25</t>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>10:38</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>1 överblommad</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6984,72 +6959,69 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Daniel Alexandersson</t>
+          <t>Milada Alexandersson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Daniel Alexandersson</t>
+          <t>Milada Alexandersson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131714430</v>
+        <v>129338834</v>
       </c>
       <c r="B55" t="n">
-        <v>58109</v>
+        <v>99118</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr"/>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Hundviken, Dlr</t>
+          <t>Hundviken, Hundviken, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>525732</v>
+        <v>525715</v>
       </c>
       <c r="R55" t="n">
-        <v>6716237</v>
+        <v>6716181</v>
       </c>
       <c r="S55" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7073,17 +7045,22 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Talltita är uppenbarligen bofast i området. Varje helg observeras ett par som är del av meståg som drar igenom skogen i jakt på föda.</t>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7098,72 +7075,74 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Daniel Alexandersson</t>
+          <t>Milada Alexandersson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Daniel Alexandersson</t>
+          <t>Milada Alexandersson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131714363</v>
+        <v>129338899</v>
       </c>
       <c r="B56" t="n">
-        <v>58109</v>
+        <v>99118</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Hundviken, Dlr</t>
+          <t>Hundviken, Hundviken, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>525686</v>
+        <v>525712</v>
       </c>
       <c r="R56" t="n">
-        <v>6716226</v>
+        <v>6716201</v>
       </c>
       <c r="S56" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7187,12 +7166,22 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7207,72 +7196,69 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Daniel Alexandersson</t>
+          <t>Milada Alexandersson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Daniel Alexandersson</t>
+          <t>Milada Alexandersson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>131714401</v>
+        <v>129339191</v>
       </c>
       <c r="B57" t="n">
-        <v>58109</v>
+        <v>99118</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr"/>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Hundviken, Dlr</t>
+          <t>Hundviken, Hundviken, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>525613</v>
+        <v>525746</v>
       </c>
       <c r="R57" t="n">
-        <v>6716157</v>
+        <v>6716215</v>
       </c>
       <c r="S57" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7296,17 +7282,22 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Upptäckt först med app i samband med promenad längs vägen. Sedan observeras två individer.</t>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7321,22 +7312,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Daniel Alexandersson</t>
+          <t>Milada Alexandersson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Daniel Alexandersson</t>
+          <t>Milada Alexandersson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>131822536</v>
+        <v>129339235</v>
       </c>
       <c r="B58" t="n">
-        <v>99098</v>
+        <v>99118</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7366,11 +7357,6 @@
           <t>10</t>
         </is>
       </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K58" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -7382,13 +7368,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>525573</v>
+        <v>525757</v>
       </c>
       <c r="R58" t="n">
-        <v>6716073</v>
+        <v>6716182</v>
       </c>
       <c r="S58" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7412,22 +7398,22 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7454,57 +7440,62 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131856463</v>
+        <v>129339499</v>
       </c>
       <c r="B59" t="n">
-        <v>58109</v>
+        <v>99118</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Hundviken, Dlr</t>
+          <t>Hundviken, Hundviken, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>525687</v>
+        <v>525771</v>
       </c>
       <c r="R59" t="n">
-        <v>6716204</v>
+        <v>6716245</v>
       </c>
       <c r="S59" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7528,27 +7519,27 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Ser två stycken talltitor och identifierar med Merlin app</t>
+          <t>Spridda över ca 0,5 m2</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7575,7 +7566,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131985054</v>
+        <v>129339551</v>
       </c>
       <c r="B60" t="n">
         <v>99118</v>
@@ -7605,7 +7596,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -7624,13 +7615,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>525629</v>
+        <v>525769</v>
       </c>
       <c r="R60" t="n">
-        <v>6716057</v>
+        <v>6716224</v>
       </c>
       <c r="S60" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7654,22 +7645,22 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7696,7 +7687,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131985410</v>
+        <v>129340627</v>
       </c>
       <c r="B61" t="n">
         <v>99118</v>
@@ -7726,7 +7717,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -7745,13 +7736,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>525611</v>
+        <v>525709</v>
       </c>
       <c r="R61" t="n">
-        <v>6716076</v>
+        <v>6716198</v>
       </c>
       <c r="S61" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7775,12 +7766,22 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7807,7 +7808,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131985295</v>
+        <v>129340696</v>
       </c>
       <c r="B62" t="n">
         <v>99118</v>
@@ -7837,7 +7838,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -7845,21 +7846,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Hundviken, Hundviken, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>525591</v>
+        <v>525672</v>
       </c>
       <c r="R62" t="n">
-        <v>6716100</v>
+        <v>6716190</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7886,22 +7882,27 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>11:59</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>På stenblock! 2 överblommade</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7925,6 +7926,940 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>130016660</v>
+      </c>
+      <c r="B63" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Hundviken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>525602</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6716070</v>
+      </c>
+      <c r="S63" t="n">
+        <v>5</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Aspeboda</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>13:42</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>13:42</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Milada Alexandersson</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Milada Alexandersson</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>131821961</v>
+      </c>
+      <c r="B64" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Hundviken, Hundviken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>525563</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6716039</v>
+      </c>
+      <c r="S64" t="n">
+        <v>5</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Aspeboda</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>14:41</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>14:41</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Milada Alexandersson</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Milada Alexandersson</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>131822536</v>
+      </c>
+      <c r="B65" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Hundviken, Hundviken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>525573</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6716073</v>
+      </c>
+      <c r="S65" t="n">
+        <v>5</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Aspeboda</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Milada Alexandersson</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Milada Alexandersson</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>131823068</v>
+      </c>
+      <c r="B66" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Hundviken, Hundviken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>525554</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6716042</v>
+      </c>
+      <c r="S66" t="n">
+        <v>5</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Aspeboda</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>15:11</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>15:11</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Milada Alexandersson</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Milada Alexandersson</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>131985054</v>
+      </c>
+      <c r="B67" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Hundviken, Hundviken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>525629</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6716057</v>
+      </c>
+      <c r="S67" t="n">
+        <v>5</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Aspeboda</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Milada Alexandersson</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Milada Alexandersson</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>131985295</v>
+      </c>
+      <c r="B68" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Hundviken, Hundviken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>525591</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6716100</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Aspeboda</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Milada Alexandersson</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Milada Alexandersson</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>131985410</v>
+      </c>
+      <c r="B69" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Hundviken, Hundviken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>525611</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6716076</v>
+      </c>
+      <c r="S69" t="n">
+        <v>5</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Aspeboda</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Milada Alexandersson</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Milada Alexandersson</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>130044041</v>
+      </c>
+      <c r="B70" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Hundviken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>525776</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6716252</v>
+      </c>
+      <c r="S70" t="n">
+        <v>25</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Aspeboda</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF70" t="inlineStr"/>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Daniel Alexandersson</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Daniel Alexandersson</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 52871-2025 artfynd.xlsx
+++ b/artfynd/A 52871-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY70"/>
+  <dimension ref="A1:AY73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3513,42 +3513,42 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127313556</v>
+        <v>134681064</v>
       </c>
       <c r="B27" t="n">
-        <v>99118</v>
+        <v>99112</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -3556,24 +3556,19 @@
           <t>blomning</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Hundviken, Hundviken, Dlr</t>
+          <t>Hundviken, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>525685</v>
+        <v>525602</v>
       </c>
       <c r="R27" t="n">
-        <v>6716175</v>
+        <v>6716070</v>
       </c>
       <c r="S27" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3597,22 +3592,27 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>17:57</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Minst 20 stycken blommande</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3639,62 +3639,62 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127314167</v>
+        <v>134681110</v>
       </c>
       <c r="B28" t="n">
-        <v>99118</v>
+        <v>99112</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Hundviken, Hundviken, Dlr</t>
+          <t>Åkergroda, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>525686</v>
+        <v>525655</v>
       </c>
       <c r="R28" t="n">
-        <v>6716155</v>
+        <v>6716145</v>
       </c>
       <c r="S28" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3718,22 +3718,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3760,37 +3760,37 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127314541</v>
+        <v>134681177</v>
       </c>
       <c r="B29" t="n">
-        <v>99118</v>
+        <v>99112</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3800,27 +3800,22 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Hundviken, Hundviken, Dlr</t>
+          <t>Åkergroda, Åkergroda, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>525690</v>
+        <v>525633</v>
       </c>
       <c r="R29" t="n">
-        <v>6716175</v>
+        <v>6716115</v>
       </c>
       <c r="S29" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3844,22 +3839,27 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>18:07</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Sumpmark</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3886,7 +3886,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127314992</v>
+        <v>127313556</v>
       </c>
       <c r="B30" t="n">
         <v>99118</v>
@@ -3916,17 +3916,17 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -3940,10 +3940,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>525694</v>
+        <v>525685</v>
       </c>
       <c r="R30" t="n">
-        <v>6716178</v>
+        <v>6716175</v>
       </c>
       <c r="S30" t="n">
         <v>1</v>
@@ -3975,7 +3975,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3985,7 +3985,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4012,7 +4012,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127315125</v>
+        <v>127314167</v>
       </c>
       <c r="B31" t="n">
         <v>99118</v>
@@ -4045,14 +4045,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -4066,10 +4061,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>525684</v>
+        <v>525686</v>
       </c>
       <c r="R31" t="n">
-        <v>6716162</v>
+        <v>6716155</v>
       </c>
       <c r="S31" t="n">
         <v>1</v>
@@ -4101,7 +4096,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4111,7 +4106,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4138,7 +4133,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127315222</v>
+        <v>127314541</v>
       </c>
       <c r="B32" t="n">
         <v>99118</v>
@@ -4168,7 +4163,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4192,10 +4187,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>525682</v>
+        <v>525690</v>
       </c>
       <c r="R32" t="n">
-        <v>6716184</v>
+        <v>6716175</v>
       </c>
       <c r="S32" t="n">
         <v>1</v>
@@ -4227,7 +4222,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4237,7 +4232,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4264,7 +4259,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127315460</v>
+        <v>127314992</v>
       </c>
       <c r="B33" t="n">
         <v>99118</v>
@@ -4294,7 +4289,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -4318,10 +4313,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>525688</v>
+        <v>525694</v>
       </c>
       <c r="R33" t="n">
-        <v>6716179</v>
+        <v>6716178</v>
       </c>
       <c r="S33" t="n">
         <v>1</v>
@@ -4353,7 +4348,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4363,7 +4358,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4390,7 +4385,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127315514</v>
+        <v>127315125</v>
       </c>
       <c r="B34" t="n">
         <v>99118</v>
@@ -4420,7 +4415,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -4444,10 +4439,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>525676</v>
+        <v>525684</v>
       </c>
       <c r="R34" t="n">
-        <v>6716168</v>
+        <v>6716162</v>
       </c>
       <c r="S34" t="n">
         <v>1</v>
@@ -4479,7 +4474,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4489,7 +4484,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4516,7 +4511,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127315588</v>
+        <v>127315222</v>
       </c>
       <c r="B35" t="n">
         <v>99118</v>
@@ -4546,7 +4541,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4556,7 +4551,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -4570,10 +4565,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>525666</v>
+        <v>525682</v>
       </c>
       <c r="R35" t="n">
-        <v>6716159</v>
+        <v>6716184</v>
       </c>
       <c r="S35" t="n">
         <v>1</v>
@@ -4605,7 +4600,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4615,7 +4610,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4642,7 +4637,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127315619</v>
+        <v>127315460</v>
       </c>
       <c r="B36" t="n">
         <v>99118</v>
@@ -4672,7 +4667,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -4696,10 +4691,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>525656</v>
+        <v>525688</v>
       </c>
       <c r="R36" t="n">
-        <v>6716166</v>
+        <v>6716179</v>
       </c>
       <c r="S36" t="n">
         <v>1</v>
@@ -4731,7 +4726,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4741,7 +4736,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4768,7 +4763,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127315716</v>
+        <v>127315514</v>
       </c>
       <c r="B37" t="n">
         <v>99118</v>
@@ -4798,7 +4793,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -4822,10 +4817,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>525670</v>
+        <v>525676</v>
       </c>
       <c r="R37" t="n">
-        <v>6716189</v>
+        <v>6716168</v>
       </c>
       <c r="S37" t="n">
         <v>1</v>
@@ -4857,7 +4852,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4867,7 +4862,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4894,7 +4889,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127316105</v>
+        <v>127315588</v>
       </c>
       <c r="B38" t="n">
         <v>99118</v>
@@ -4934,7 +4929,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -4948,10 +4943,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>525712</v>
+        <v>525666</v>
       </c>
       <c r="R38" t="n">
-        <v>6716192</v>
+        <v>6716159</v>
       </c>
       <c r="S38" t="n">
         <v>1</v>
@@ -4983,7 +4978,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4993,7 +4988,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5020,7 +5015,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127316136</v>
+        <v>127315619</v>
       </c>
       <c r="B39" t="n">
         <v>99118</v>
@@ -5060,7 +5055,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -5074,10 +5069,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>525712</v>
+        <v>525656</v>
       </c>
       <c r="R39" t="n">
-        <v>6716193</v>
+        <v>6716166</v>
       </c>
       <c r="S39" t="n">
         <v>1</v>
@@ -5109,7 +5104,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5119,7 +5114,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5146,7 +5141,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127316162</v>
+        <v>127315716</v>
       </c>
       <c r="B40" t="n">
         <v>99118</v>
@@ -5186,7 +5181,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -5200,10 +5195,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>525752</v>
+        <v>525670</v>
       </c>
       <c r="R40" t="n">
-        <v>6716206</v>
+        <v>6716189</v>
       </c>
       <c r="S40" t="n">
         <v>1</v>
@@ -5235,7 +5230,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5245,7 +5240,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5272,7 +5267,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127316228</v>
+        <v>127316105</v>
       </c>
       <c r="B41" t="n">
         <v>99118</v>
@@ -5302,7 +5297,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5326,10 +5321,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>525740</v>
+        <v>525712</v>
       </c>
       <c r="R41" t="n">
-        <v>6716244</v>
+        <v>6716192</v>
       </c>
       <c r="S41" t="n">
         <v>1</v>
@@ -5361,7 +5356,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5371,7 +5366,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5398,7 +5393,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127316295</v>
+        <v>127316136</v>
       </c>
       <c r="B42" t="n">
         <v>99118</v>
@@ -5438,7 +5433,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -5452,10 +5447,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>525743</v>
+        <v>525712</v>
       </c>
       <c r="R42" t="n">
-        <v>6716220</v>
+        <v>6716193</v>
       </c>
       <c r="S42" t="n">
         <v>1</v>
@@ -5487,7 +5482,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5497,7 +5492,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5524,7 +5519,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127316344</v>
+        <v>127316162</v>
       </c>
       <c r="B43" t="n">
         <v>99118</v>
@@ -5554,12 +5549,17 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -5573,13 +5573,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>525736</v>
+        <v>525752</v>
       </c>
       <c r="R43" t="n">
-        <v>6716217</v>
+        <v>6716206</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5608,7 +5608,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5618,7 +5618,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5645,7 +5645,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127316409</v>
+        <v>127316228</v>
       </c>
       <c r="B44" t="n">
         <v>99118</v>
@@ -5675,7 +5675,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -5699,10 +5699,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>525735</v>
+        <v>525740</v>
       </c>
       <c r="R44" t="n">
-        <v>6716213</v>
+        <v>6716244</v>
       </c>
       <c r="S44" t="n">
         <v>1</v>
@@ -5734,7 +5734,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5744,7 +5744,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5771,7 +5771,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127350965</v>
+        <v>127316295</v>
       </c>
       <c r="B45" t="n">
         <v>99118</v>
@@ -5801,12 +5801,22 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5815,10 +5825,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>525685</v>
+        <v>525743</v>
       </c>
       <c r="R45" t="n">
-        <v>6716229</v>
+        <v>6716220</v>
       </c>
       <c r="S45" t="n">
         <v>1</v>
@@ -5845,27 +5855,22 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-08-09</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>18:49</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-08-09</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>18:49</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>1 stjälke</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5892,7 +5897,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127351108</v>
+        <v>127316344</v>
       </c>
       <c r="B46" t="n">
         <v>99118</v>
@@ -5922,12 +5927,17 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5936,13 +5946,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>525674</v>
+        <v>525736</v>
       </c>
       <c r="R46" t="n">
-        <v>6716190</v>
+        <v>6716217</v>
       </c>
       <c r="S46" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5966,27 +5976,22 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-08-09</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>18:56</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-08-09</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>18:56</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>1 stjälke</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6013,7 +6018,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127351240</v>
+        <v>127316409</v>
       </c>
       <c r="B47" t="n">
         <v>99118</v>
@@ -6043,7 +6048,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -6051,19 +6056,29 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Hundviken, Hundviken, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>525680</v>
+        <v>525735</v>
       </c>
       <c r="R47" t="n">
-        <v>6716185</v>
+        <v>6716213</v>
       </c>
       <c r="S47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6087,22 +6102,22 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-08-09</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-08-09</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6129,7 +6144,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127351377</v>
+        <v>127350965</v>
       </c>
       <c r="B48" t="n">
         <v>99118</v>
@@ -6159,7 +6174,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -6173,10 +6188,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>525680</v>
+        <v>525685</v>
       </c>
       <c r="R48" t="n">
-        <v>6716172</v>
+        <v>6716229</v>
       </c>
       <c r="S48" t="n">
         <v>1</v>
@@ -6208,7 +6223,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>19:07</t>
+          <t>18:49</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6218,7 +6233,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>19:07</t>
+          <t>18:49</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
@@ -6250,7 +6265,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127351427</v>
+        <v>127351108</v>
       </c>
       <c r="B49" t="n">
         <v>99118</v>
@@ -6294,10 +6309,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>525690</v>
+        <v>525674</v>
       </c>
       <c r="R49" t="n">
-        <v>6716183</v>
+        <v>6716190</v>
       </c>
       <c r="S49" t="n">
         <v>1</v>
@@ -6329,7 +6344,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>18:56</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6339,7 +6354,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>18:56</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
@@ -6371,7 +6386,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127351465</v>
+        <v>127351240</v>
       </c>
       <c r="B50" t="n">
         <v>99118</v>
@@ -6401,12 +6416,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -6415,13 +6430,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>525676</v>
+        <v>525680</v>
       </c>
       <c r="R50" t="n">
-        <v>6716177</v>
+        <v>6716185</v>
       </c>
       <c r="S50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6450,7 +6465,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>19:13</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6460,12 +6475,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>19:13</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>2 stjälkar</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6492,7 +6502,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127351678</v>
+        <v>127351377</v>
       </c>
       <c r="B51" t="n">
         <v>99118</v>
@@ -6522,7 +6532,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -6536,13 +6546,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>525682</v>
+        <v>525680</v>
       </c>
       <c r="R51" t="n">
-        <v>6716183</v>
+        <v>6716172</v>
       </c>
       <c r="S51" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6571,7 +6581,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>19:23</t>
+          <t>19:07</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6581,7 +6591,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>19:23</t>
+          <t>19:07</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>1 stjälke</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6608,7 +6623,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129338511</v>
+        <v>127351427</v>
       </c>
       <c r="B52" t="n">
         <v>99118</v>
@@ -6638,12 +6653,12 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -6652,13 +6667,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>525680</v>
+        <v>525690</v>
       </c>
       <c r="R52" t="n">
-        <v>6716143</v>
+        <v>6716183</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6682,27 +6697,27 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-08-09</t>
         </is>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-08-09</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Ca 20 bladrosetter 1 överblommade</t>
+          <t>1 stjälke</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6729,7 +6744,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129338590</v>
+        <v>127351465</v>
       </c>
       <c r="B53" t="n">
         <v>99118</v>
@@ -6759,12 +6774,12 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -6773,10 +6788,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>525673</v>
+        <v>525676</v>
       </c>
       <c r="R53" t="n">
-        <v>6716152</v>
+        <v>6716177</v>
       </c>
       <c r="S53" t="n">
         <v>1</v>
@@ -6803,22 +6818,27 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-08-09</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>19:13</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-08-09</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>19:13</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>2 stjälkar</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6845,7 +6865,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129338657</v>
+        <v>127351678</v>
       </c>
       <c r="B54" t="n">
         <v>99118</v>
@@ -6875,17 +6895,12 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -6894,13 +6909,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>525677</v>
+        <v>525682</v>
       </c>
       <c r="R54" t="n">
-        <v>6716163</v>
+        <v>6716183</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6924,27 +6939,22 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-08-09</t>
         </is>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>19:23</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-08-09</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>10:38</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>1 överblommad</t>
+          <t>19:23</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6971,7 +6981,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129338834</v>
+        <v>129338511</v>
       </c>
       <c r="B55" t="n">
         <v>99118</v>
@@ -7001,7 +7011,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -7015,10 +7025,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>525715</v>
+        <v>525680</v>
       </c>
       <c r="R55" t="n">
-        <v>6716181</v>
+        <v>6716143</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7050,7 +7060,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7060,7 +7070,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:31</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Ca 20 bladrosetter 1 överblommade</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7087,7 +7102,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129338899</v>
+        <v>129338590</v>
       </c>
       <c r="B56" t="n">
         <v>99118</v>
@@ -7117,17 +7132,12 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>dm²</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -7136,13 +7146,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>525712</v>
+        <v>525673</v>
       </c>
       <c r="R56" t="n">
-        <v>6716201</v>
+        <v>6716152</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7171,7 +7181,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7181,7 +7191,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7208,7 +7218,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129339191</v>
+        <v>129338657</v>
       </c>
       <c r="B57" t="n">
         <v>99118</v>
@@ -7238,7 +7248,12 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -7252,10 +7267,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>525746</v>
+        <v>525677</v>
       </c>
       <c r="R57" t="n">
-        <v>6716215</v>
+        <v>6716163</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7287,7 +7302,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7297,7 +7312,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:38</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>1 överblommad</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7324,7 +7344,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129339235</v>
+        <v>129338834</v>
       </c>
       <c r="B58" t="n">
         <v>99118</v>
@@ -7354,7 +7374,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -7368,10 +7388,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>525757</v>
+        <v>525715</v>
       </c>
       <c r="R58" t="n">
-        <v>6716182</v>
+        <v>6716181</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7403,7 +7423,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7413,7 +7433,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7440,7 +7460,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129339499</v>
+        <v>129338899</v>
       </c>
       <c r="B59" t="n">
         <v>99118</v>
@@ -7470,12 +7490,12 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -7489,10 +7509,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>525771</v>
+        <v>525712</v>
       </c>
       <c r="R59" t="n">
-        <v>6716245</v>
+        <v>6716201</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7524,7 +7544,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7534,12 +7554,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>11:09</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Spridda över ca 0,5 m2</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7566,7 +7581,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129339551</v>
+        <v>129339191</v>
       </c>
       <c r="B60" t="n">
         <v>99118</v>
@@ -7596,12 +7611,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -7615,10 +7625,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>525769</v>
+        <v>525746</v>
       </c>
       <c r="R60" t="n">
-        <v>6716224</v>
+        <v>6716215</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7650,7 +7660,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7660,7 +7670,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7687,7 +7697,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129340627</v>
+        <v>129339235</v>
       </c>
       <c r="B61" t="n">
         <v>99118</v>
@@ -7717,12 +7727,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -7736,10 +7741,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>525709</v>
+        <v>525757</v>
       </c>
       <c r="R61" t="n">
-        <v>6716198</v>
+        <v>6716182</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7771,7 +7776,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7781,7 +7786,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7808,7 +7813,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129340696</v>
+        <v>129339499</v>
       </c>
       <c r="B62" t="n">
         <v>99118</v>
@@ -7838,7 +7843,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -7846,16 +7851,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Hundviken, Hundviken, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>525672</v>
+        <v>525771</v>
       </c>
       <c r="R62" t="n">
-        <v>6716190</v>
+        <v>6716245</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7887,7 +7897,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7897,12 +7907,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>På stenblock! 2 överblommade</t>
+          <t>Spridda över ca 0,5 m2</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7929,7 +7939,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>130016660</v>
+        <v>129339551</v>
       </c>
       <c r="B63" t="n">
         <v>99118</v>
@@ -7967,19 +7977,24 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Hundviken, Dlr</t>
+          <t>Hundviken, Hundviken, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>525602</v>
+        <v>525769</v>
       </c>
       <c r="R63" t="n">
-        <v>6716070</v>
+        <v>6716224</v>
       </c>
       <c r="S63" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -8003,22 +8018,22 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2025-12-07</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2025-12-07</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8045,10 +8060,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>131821961</v>
+        <v>129340627</v>
       </c>
       <c r="B64" t="n">
-        <v>99195</v>
+        <v>99118</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8075,7 +8090,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -8094,13 +8109,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>525563</v>
+        <v>525709</v>
       </c>
       <c r="R64" t="n">
-        <v>6716039</v>
+        <v>6716198</v>
       </c>
       <c r="S64" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8124,22 +8139,22 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8166,10 +8181,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>131822536</v>
+        <v>129340696</v>
       </c>
       <c r="B65" t="n">
-        <v>99195</v>
+        <v>99118</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8196,7 +8211,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -8204,24 +8219,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Hundviken, Hundviken, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>525573</v>
+        <v>525672</v>
       </c>
       <c r="R65" t="n">
-        <v>6716073</v>
+        <v>6716190</v>
       </c>
       <c r="S65" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8245,22 +8255,27 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>11:59</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>På stenblock! 2 överblommade</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8287,10 +8302,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>131823068</v>
+        <v>130016660</v>
       </c>
       <c r="B66" t="n">
-        <v>99195</v>
+        <v>99118</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8325,21 +8340,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Hundviken, Hundviken, Dlr</t>
+          <t>Hundviken, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>525554</v>
+        <v>525602</v>
       </c>
       <c r="R66" t="n">
-        <v>6716042</v>
+        <v>6716070</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -8366,22 +8376,22 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2025-12-07</t>
         </is>
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2025-12-07</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8408,7 +8418,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>131985054</v>
+        <v>131821961</v>
       </c>
       <c r="B67" t="n">
         <v>99195</v>
@@ -8438,7 +8448,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -8457,10 +8467,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>525629</v>
+        <v>525563</v>
       </c>
       <c r="R67" t="n">
-        <v>6716057</v>
+        <v>6716039</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -8487,22 +8497,22 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8529,7 +8539,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>131985295</v>
+        <v>131822536</v>
       </c>
       <c r="B68" t="n">
         <v>99195</v>
@@ -8578,13 +8588,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>525591</v>
+        <v>525573</v>
       </c>
       <c r="R68" t="n">
-        <v>6716100</v>
+        <v>6716073</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8608,22 +8618,22 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8650,7 +8660,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>131985410</v>
+        <v>131823068</v>
       </c>
       <c r="B69" t="n">
         <v>99195</v>
@@ -8680,7 +8690,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -8699,10 +8709,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>525611</v>
+        <v>525554</v>
       </c>
       <c r="R69" t="n">
-        <v>6716076</v>
+        <v>6716042</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -8729,12 +8739,22 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8761,52 +8781,62 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>130044041</v>
+        <v>131985054</v>
       </c>
       <c r="B70" t="n">
-        <v>97989</v>
+        <v>99195</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Hundviken, Dlr</t>
+          <t>Hundviken, Hundviken, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>525776</v>
+        <v>525629</v>
       </c>
       <c r="R70" t="n">
-        <v>6716252</v>
+        <v>6716057</v>
       </c>
       <c r="S70" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8830,12 +8860,22 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8844,22 +8884,355 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
+          <t>Milada Alexandersson</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Milada Alexandersson</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>131985295</v>
+      </c>
+      <c r="B71" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Hundviken, Hundviken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>525591</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6716100</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Aspeboda</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Milada Alexandersson</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Milada Alexandersson</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>131985410</v>
+      </c>
+      <c r="B72" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Hundviken, Hundviken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>525611</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6716076</v>
+      </c>
+      <c r="S72" t="n">
+        <v>5</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Aspeboda</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Milada Alexandersson</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Milada Alexandersson</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>130044041</v>
+      </c>
+      <c r="B73" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Hundviken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>525776</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6716252</v>
+      </c>
+      <c r="S73" t="n">
+        <v>25</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Aspeboda</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF73" t="inlineStr"/>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
           <t>Daniel Alexandersson</t>
         </is>
       </c>
-      <c r="AX70" t="inlineStr">
+      <c r="AX73" t="inlineStr">
         <is>
           <t>Daniel Alexandersson</t>
         </is>
       </c>
-      <c r="AY70" t="inlineStr"/>
+      <c r="AY73" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 52871-2025 artfynd.xlsx
+++ b/artfynd/A 52871-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY73"/>
+  <dimension ref="A1:AY76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1729,10 +1729,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129938268</v>
+        <v>134719140</v>
       </c>
       <c r="B11" t="n">
-        <v>58112</v>
+        <v>57391</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1740,21 +1740,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103020</v>
+        <v>102961</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Drillsnäppa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Actitis hypoleucos</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1762,24 +1762,29 @@
           <t>2</t>
         </is>
       </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>besöker bebott bo</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Stående död tall, Dlr</t>
+          <t>Hundviken, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>525775</v>
+        <v>525687</v>
       </c>
       <c r="R11" t="n">
-        <v>6716218</v>
+        <v>6716204</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1803,12 +1808,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-04-11</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-04-11</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1835,7 +1840,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129979175</v>
+        <v>129938268</v>
       </c>
       <c r="B12" t="n">
         <v>58112</v>
@@ -1863,10 +1868,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1875,13 +1884,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>525766</v>
+        <v>525775</v>
       </c>
       <c r="R12" t="n">
-        <v>6716251</v>
+        <v>6716218</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1937,10 +1946,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131158127</v>
+        <v>129979175</v>
       </c>
       <c r="B13" t="n">
-        <v>58114</v>
+        <v>58112</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1948,46 +1957,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>103020</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
           <t>upprörd, varnande</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Hundviken, Dlr</t>
+          <t>Stående död tall, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>525695</v>
+        <v>525766</v>
       </c>
       <c r="R13" t="n">
-        <v>6716177</v>
+        <v>6716251</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2014,12 +2016,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-01-11</t>
+          <t>2025-04-11</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-01-11</t>
+          <t>2025-04-11</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2034,19 +2036,19 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Daniel Alexandersson</t>
+          <t>Milada Alexandersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Daniel Alexandersson</t>
+          <t>Milada Alexandersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131158205</v>
+        <v>131158127</v>
       </c>
       <c r="B14" t="n">
         <v>58114</v>
@@ -2093,10 +2095,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>525731</v>
+        <v>525695</v>
       </c>
       <c r="R14" t="n">
-        <v>6716197</v>
+        <v>6716177</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2123,12 +2125,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-01-11</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-01-11</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2155,7 +2157,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131158214</v>
+        <v>131158205</v>
       </c>
       <c r="B15" t="n">
         <v>58114</v>
@@ -2202,10 +2204,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>525566</v>
+        <v>525731</v>
       </c>
       <c r="R15" t="n">
-        <v>6716104</v>
+        <v>6716197</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2232,12 +2234,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-01-25</t>
+          <t>2026-02-08</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-01-25</t>
+          <t>2026-02-08</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2264,7 +2266,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131158283</v>
+        <v>131158214</v>
       </c>
       <c r="B16" t="n">
         <v>58114</v>
@@ -2311,10 +2313,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>525550</v>
+        <v>525566</v>
       </c>
       <c r="R16" t="n">
-        <v>6716117</v>
+        <v>6716104</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2341,17 +2343,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-25</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Hört fågeln och registrerat med app.</t>
+          <t>2026-01-25</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2378,7 +2375,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131158288</v>
+        <v>131158283</v>
       </c>
       <c r="B17" t="n">
         <v>58114</v>
@@ -2425,10 +2422,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>525513</v>
+        <v>525550</v>
       </c>
       <c r="R17" t="n">
-        <v>6716073</v>
+        <v>6716117</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2465,7 +2462,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Hört och registrerat med app</t>
+          <t>Hört fågeln och registrerat med app.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2492,10 +2489,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131714363</v>
+        <v>131158288</v>
       </c>
       <c r="B18" t="n">
-        <v>58136</v>
+        <v>58114</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2539,10 +2536,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>525686</v>
+        <v>525513</v>
       </c>
       <c r="R18" t="n">
-        <v>6716226</v>
+        <v>6716073</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2569,12 +2566,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Hört och registrerat med app</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2601,7 +2603,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131714401</v>
+        <v>131714363</v>
       </c>
       <c r="B19" t="n">
         <v>58136</v>
@@ -2631,7 +2633,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -2648,10 +2650,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>525613</v>
+        <v>525686</v>
       </c>
       <c r="R19" t="n">
-        <v>6716157</v>
+        <v>6716226</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2678,17 +2680,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Upptäckt först med app i samband med promenad längs vägen. Sedan observeras två individer.</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2715,7 +2712,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131714430</v>
+        <v>131714401</v>
       </c>
       <c r="B20" t="n">
         <v>58136</v>
@@ -2762,10 +2759,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>525732</v>
+        <v>525613</v>
       </c>
       <c r="R20" t="n">
-        <v>6716237</v>
+        <v>6716157</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2792,17 +2789,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Talltita är uppenbarligen bofast i området. Varje helg observeras ett par som är del av meståg som drar igenom skogen i jakt på föda.</t>
+          <t>Upptäckt först med app i samband med promenad längs vägen. Sedan observeras två individer.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2829,7 +2826,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131856463</v>
+        <v>131714430</v>
       </c>
       <c r="B21" t="n">
         <v>58136</v>
@@ -2862,21 +2859,24 @@
           <t>2</t>
         </is>
       </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
           <t>upprörd, varnande</t>
         </is>
       </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Hundviken, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>525687</v>
+        <v>525732</v>
       </c>
       <c r="R21" t="n">
-        <v>6716204</v>
+        <v>6716237</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2903,27 +2903,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>10:00</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>10:00</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ser två stycken talltitor och identifierar med Merlin app</t>
+          <t>Talltita är uppenbarligen bofast i området. Varje helg observeras ett par som är del av meståg som drar igenom skogen i jakt på föda.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2938,65 +2928,69 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Milada Alexandersson</t>
+          <t>Daniel Alexandersson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Milada Alexandersson</t>
+          <t>Daniel Alexandersson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129339605</v>
+        <v>131856463</v>
       </c>
       <c r="B22" t="n">
-        <v>8455</v>
+        <v>58136</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Hundviken, Hundviken, Dlr</t>
+          <t>Hundviken, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>525780</v>
+        <v>525687</v>
       </c>
       <c r="R22" t="n">
-        <v>6716226</v>
+        <v>6716204</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3020,22 +3014,27 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ser två stycken talltitor och identifierar med Merlin app</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3062,7 +3061,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129340891</v>
+        <v>129339605</v>
       </c>
       <c r="B23" t="n">
         <v>8455</v>
@@ -3102,10 +3101,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>525685</v>
+        <v>525780</v>
       </c>
       <c r="R23" t="n">
-        <v>6716122</v>
+        <v>6716226</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3137,7 +3136,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3147,7 +3146,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3174,10 +3173,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130044230</v>
+        <v>129340891</v>
       </c>
       <c r="B24" t="n">
-        <v>58817</v>
+        <v>8455</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3185,50 +3184,42 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>208249</v>
+        <v>106545</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Intill väg, Dlr</t>
+          <t>Hundviken, Hundviken, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>525653</v>
+        <v>525685</v>
       </c>
       <c r="R24" t="n">
-        <v>6716143</v>
+        <v>6716122</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3252,17 +3243,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-08-09</t>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-08-09</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Stor för att vara vanlig groda. Närmast paddstorlek.</t>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3271,29 +3267,28 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Daniel Alexandersson</t>
+          <t>Milada Alexandersson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Daniel Alexandersson</t>
+          <t>Milada Alexandersson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129727312</v>
+        <v>130044230</v>
       </c>
       <c r="B25" t="n">
-        <v>58815</v>
+        <v>58817</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3301,21 +3296,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>208250</v>
+        <v>208249</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3323,24 +3318,28 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Åkergroda, Dlr</t>
+          <t>Intill väg, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>525655</v>
+        <v>525653</v>
       </c>
       <c r="R25" t="n">
-        <v>6716145</v>
+        <v>6716143</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3364,17 +3363,17 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-08-17</t>
+          <t>2025-08-09</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-08-17</t>
+          <t>2025-08-09</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Fotad och eftergranskad av grodexpert</t>
+          <t>Stor för att vara vanlig groda. Närmast paddstorlek.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3390,22 +3389,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Milada Alexandersson</t>
+          <t>Daniel Alexandersson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Milada Alexandersson</t>
+          <t>Daniel Alexandersson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130022082</v>
+        <v>129727312</v>
       </c>
       <c r="B26" t="n">
-        <v>56884</v>
+        <v>58815</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3413,21 +3412,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>208255</v>
+        <v>208250</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Zootoca vivipara</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Jacquin, 1787)</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3435,28 +3434,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Intill väg, Dlr</t>
+          <t>Åkergroda, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>525632</v>
+        <v>525655</v>
       </c>
       <c r="R26" t="n">
-        <v>6716152</v>
+        <v>6716145</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3480,12 +3475,17 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-08-17</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Fotad och eftergranskad av grodexpert</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3501,22 +3501,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Daniel Alexandersson</t>
+          <t>Milada Alexandersson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Daniel Alexandersson</t>
+          <t>Milada Alexandersson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>134681064</v>
+        <v>130022082</v>
       </c>
       <c r="B27" t="n">
-        <v>99112</v>
+        <v>56884</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3524,48 +3524,47 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>219790</v>
+        <v>208255</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Zootoca vivipara</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Jacquin, 1787)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Hundviken, Dlr</t>
+          <t>Intill väg, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>525602</v>
+        <v>525632</v>
       </c>
       <c r="R27" t="n">
-        <v>6716070</v>
+        <v>6716152</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3592,27 +3591,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>17:57</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>17:57</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Minst 20 stycken blommande</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3621,25 +3605,26 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Milada Alexandersson</t>
+          <t>Daniel Alexandersson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Milada Alexandersson</t>
+          <t>Daniel Alexandersson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>134681110</v>
+        <v>134681064</v>
       </c>
       <c r="B28" t="n">
         <v>99112</v>
@@ -3669,7 +3654,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3684,17 +3669,17 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Åkergroda, Dlr</t>
+          <t>Hundviken, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>525655</v>
+        <v>525602</v>
       </c>
       <c r="R28" t="n">
-        <v>6716145</v>
+        <v>6716070</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3723,7 +3708,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3733,7 +3718,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>17:57</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Minst 20 stycken blommande</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3760,7 +3750,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>134681177</v>
+        <v>134681110</v>
       </c>
       <c r="B29" t="n">
         <v>99112</v>
@@ -3790,7 +3780,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3805,17 +3795,17 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Åkergroda, Åkergroda, Dlr</t>
+          <t>Åkergroda, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>525633</v>
+        <v>525655</v>
       </c>
       <c r="R29" t="n">
-        <v>6716115</v>
+        <v>6716145</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3844,7 +3834,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3854,12 +3844,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>18:07</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Sumpmark</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3886,42 +3871,42 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127313556</v>
+        <v>134681177</v>
       </c>
       <c r="B30" t="n">
-        <v>99118</v>
+        <v>99112</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -3929,24 +3914,19 @@
           <t>blomning</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Hundviken, Hundviken, Dlr</t>
+          <t>Åkergroda, Åkergroda, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>525685</v>
+        <v>525633</v>
       </c>
       <c r="R30" t="n">
-        <v>6716175</v>
+        <v>6716115</v>
       </c>
       <c r="S30" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3970,22 +3950,27 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>18:07</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Sumpmark</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4012,47 +3997,47 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127314167</v>
+        <v>134718812</v>
       </c>
       <c r="B31" t="n">
-        <v>99118</v>
+        <v>99112</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4061,13 +4046,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>525686</v>
+        <v>525525</v>
       </c>
       <c r="R31" t="n">
-        <v>6716155</v>
+        <v>6716117</v>
       </c>
       <c r="S31" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4091,22 +4076,22 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4133,37 +4118,37 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127314541</v>
+        <v>134718884</v>
       </c>
       <c r="B32" t="n">
-        <v>99118</v>
+        <v>99112</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4173,12 +4158,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4187,13 +4167,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>525690</v>
+        <v>525588</v>
       </c>
       <c r="R32" t="n">
-        <v>6716175</v>
+        <v>6716154</v>
       </c>
       <c r="S32" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4217,22 +4197,22 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4259,7 +4239,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127314992</v>
+        <v>127313556</v>
       </c>
       <c r="B33" t="n">
         <v>99118</v>
@@ -4289,17 +4269,17 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -4313,10 +4293,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>525694</v>
+        <v>525685</v>
       </c>
       <c r="R33" t="n">
-        <v>6716178</v>
+        <v>6716175</v>
       </c>
       <c r="S33" t="n">
         <v>1</v>
@@ -4348,7 +4328,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4358,7 +4338,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4385,7 +4365,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127315125</v>
+        <v>127314167</v>
       </c>
       <c r="B34" t="n">
         <v>99118</v>
@@ -4418,14 +4398,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -4439,10 +4414,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>525684</v>
+        <v>525686</v>
       </c>
       <c r="R34" t="n">
-        <v>6716162</v>
+        <v>6716155</v>
       </c>
       <c r="S34" t="n">
         <v>1</v>
@@ -4474,7 +4449,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4484,7 +4459,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4511,7 +4486,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127315222</v>
+        <v>127314541</v>
       </c>
       <c r="B35" t="n">
         <v>99118</v>
@@ -4541,7 +4516,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4565,10 +4540,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>525682</v>
+        <v>525690</v>
       </c>
       <c r="R35" t="n">
-        <v>6716184</v>
+        <v>6716175</v>
       </c>
       <c r="S35" t="n">
         <v>1</v>
@@ -4600,7 +4575,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4610,7 +4585,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4637,7 +4612,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127315460</v>
+        <v>127314992</v>
       </c>
       <c r="B36" t="n">
         <v>99118</v>
@@ -4667,7 +4642,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -4691,10 +4666,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>525688</v>
+        <v>525694</v>
       </c>
       <c r="R36" t="n">
-        <v>6716179</v>
+        <v>6716178</v>
       </c>
       <c r="S36" t="n">
         <v>1</v>
@@ -4726,7 +4701,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4736,7 +4711,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4763,7 +4738,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127315514</v>
+        <v>127315125</v>
       </c>
       <c r="B37" t="n">
         <v>99118</v>
@@ -4793,7 +4768,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -4817,10 +4792,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>525676</v>
+        <v>525684</v>
       </c>
       <c r="R37" t="n">
-        <v>6716168</v>
+        <v>6716162</v>
       </c>
       <c r="S37" t="n">
         <v>1</v>
@@ -4852,7 +4827,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4862,7 +4837,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4889,7 +4864,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127315588</v>
+        <v>127315222</v>
       </c>
       <c r="B38" t="n">
         <v>99118</v>
@@ -4919,7 +4894,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -4929,7 +4904,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -4943,10 +4918,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>525666</v>
+        <v>525682</v>
       </c>
       <c r="R38" t="n">
-        <v>6716159</v>
+        <v>6716184</v>
       </c>
       <c r="S38" t="n">
         <v>1</v>
@@ -4978,7 +4953,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4988,7 +4963,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5015,7 +4990,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127315619</v>
+        <v>127315460</v>
       </c>
       <c r="B39" t="n">
         <v>99118</v>
@@ -5045,7 +5020,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -5069,10 +5044,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>525656</v>
+        <v>525688</v>
       </c>
       <c r="R39" t="n">
-        <v>6716166</v>
+        <v>6716179</v>
       </c>
       <c r="S39" t="n">
         <v>1</v>
@@ -5104,7 +5079,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5114,7 +5089,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5141,7 +5116,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127315716</v>
+        <v>127315514</v>
       </c>
       <c r="B40" t="n">
         <v>99118</v>
@@ -5171,7 +5146,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -5195,10 +5170,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>525670</v>
+        <v>525676</v>
       </c>
       <c r="R40" t="n">
-        <v>6716189</v>
+        <v>6716168</v>
       </c>
       <c r="S40" t="n">
         <v>1</v>
@@ -5230,7 +5205,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5240,7 +5215,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5267,7 +5242,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127316105</v>
+        <v>127315588</v>
       </c>
       <c r="B41" t="n">
         <v>99118</v>
@@ -5307,7 +5282,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -5321,10 +5296,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>525712</v>
+        <v>525666</v>
       </c>
       <c r="R41" t="n">
-        <v>6716192</v>
+        <v>6716159</v>
       </c>
       <c r="S41" t="n">
         <v>1</v>
@@ -5356,7 +5331,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5366,7 +5341,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5393,7 +5368,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127316136</v>
+        <v>127315619</v>
       </c>
       <c r="B42" t="n">
         <v>99118</v>
@@ -5433,7 +5408,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -5447,10 +5422,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>525712</v>
+        <v>525656</v>
       </c>
       <c r="R42" t="n">
-        <v>6716193</v>
+        <v>6716166</v>
       </c>
       <c r="S42" t="n">
         <v>1</v>
@@ -5482,7 +5457,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5492,7 +5467,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5519,7 +5494,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127316162</v>
+        <v>127315716</v>
       </c>
       <c r="B43" t="n">
         <v>99118</v>
@@ -5559,7 +5534,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -5573,10 +5548,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>525752</v>
+        <v>525670</v>
       </c>
       <c r="R43" t="n">
-        <v>6716206</v>
+        <v>6716189</v>
       </c>
       <c r="S43" t="n">
         <v>1</v>
@@ -5608,7 +5583,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5618,7 +5593,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5645,7 +5620,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127316228</v>
+        <v>127316105</v>
       </c>
       <c r="B44" t="n">
         <v>99118</v>
@@ -5675,7 +5650,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -5699,10 +5674,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>525740</v>
+        <v>525712</v>
       </c>
       <c r="R44" t="n">
-        <v>6716244</v>
+        <v>6716192</v>
       </c>
       <c r="S44" t="n">
         <v>1</v>
@@ -5734,7 +5709,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5744,7 +5719,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5771,7 +5746,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127316295</v>
+        <v>127316136</v>
       </c>
       <c r="B45" t="n">
         <v>99118</v>
@@ -5811,7 +5786,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -5825,10 +5800,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>525743</v>
+        <v>525712</v>
       </c>
       <c r="R45" t="n">
-        <v>6716220</v>
+        <v>6716193</v>
       </c>
       <c r="S45" t="n">
         <v>1</v>
@@ -5860,7 +5835,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5870,7 +5845,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5897,7 +5872,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127316344</v>
+        <v>127316162</v>
       </c>
       <c r="B46" t="n">
         <v>99118</v>
@@ -5927,12 +5902,17 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -5946,13 +5926,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>525736</v>
+        <v>525752</v>
       </c>
       <c r="R46" t="n">
-        <v>6716217</v>
+        <v>6716206</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5981,7 +5961,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5991,7 +5971,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6018,7 +5998,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127316409</v>
+        <v>127316228</v>
       </c>
       <c r="B47" t="n">
         <v>99118</v>
@@ -6048,7 +6028,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -6072,10 +6052,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>525735</v>
+        <v>525740</v>
       </c>
       <c r="R47" t="n">
-        <v>6716213</v>
+        <v>6716244</v>
       </c>
       <c r="S47" t="n">
         <v>1</v>
@@ -6107,7 +6087,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6117,7 +6097,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6144,7 +6124,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127350965</v>
+        <v>127316295</v>
       </c>
       <c r="B48" t="n">
         <v>99118</v>
@@ -6174,12 +6154,22 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -6188,10 +6178,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>525685</v>
+        <v>525743</v>
       </c>
       <c r="R48" t="n">
-        <v>6716229</v>
+        <v>6716220</v>
       </c>
       <c r="S48" t="n">
         <v>1</v>
@@ -6218,27 +6208,22 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-08-09</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>18:49</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-08-09</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>18:49</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>1 stjälke</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6265,7 +6250,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127351108</v>
+        <v>127316344</v>
       </c>
       <c r="B49" t="n">
         <v>99118</v>
@@ -6295,12 +6280,17 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -6309,13 +6299,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>525674</v>
+        <v>525736</v>
       </c>
       <c r="R49" t="n">
-        <v>6716190</v>
+        <v>6716217</v>
       </c>
       <c r="S49" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6339,27 +6329,22 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-08-09</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>18:56</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-08-09</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>18:56</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>1 stjälke</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6386,7 +6371,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127351240</v>
+        <v>127316409</v>
       </c>
       <c r="B50" t="n">
         <v>99118</v>
@@ -6416,7 +6401,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -6424,19 +6409,29 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Hundviken, Hundviken, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>525680</v>
+        <v>525735</v>
       </c>
       <c r="R50" t="n">
-        <v>6716185</v>
+        <v>6716213</v>
       </c>
       <c r="S50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6460,22 +6455,22 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2025-08-09</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2025-08-09</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6502,7 +6497,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127351377</v>
+        <v>127350965</v>
       </c>
       <c r="B51" t="n">
         <v>99118</v>
@@ -6532,7 +6527,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -6546,10 +6541,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>525680</v>
+        <v>525685</v>
       </c>
       <c r="R51" t="n">
-        <v>6716172</v>
+        <v>6716229</v>
       </c>
       <c r="S51" t="n">
         <v>1</v>
@@ -6581,7 +6576,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>19:07</t>
+          <t>18:49</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6591,7 +6586,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>19:07</t>
+          <t>18:49</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
@@ -6623,7 +6618,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127351427</v>
+        <v>127351108</v>
       </c>
       <c r="B52" t="n">
         <v>99118</v>
@@ -6667,10 +6662,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>525690</v>
+        <v>525674</v>
       </c>
       <c r="R52" t="n">
-        <v>6716183</v>
+        <v>6716190</v>
       </c>
       <c r="S52" t="n">
         <v>1</v>
@@ -6702,7 +6697,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>18:56</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6712,7 +6707,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>18:56</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
@@ -6744,7 +6739,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127351465</v>
+        <v>127351240</v>
       </c>
       <c r="B53" t="n">
         <v>99118</v>
@@ -6774,12 +6769,12 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -6788,13 +6783,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>525676</v>
+        <v>525680</v>
       </c>
       <c r="R53" t="n">
-        <v>6716177</v>
+        <v>6716185</v>
       </c>
       <c r="S53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6823,7 +6818,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>19:13</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6833,12 +6828,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>19:13</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>2 stjälkar</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6865,7 +6855,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127351678</v>
+        <v>127351377</v>
       </c>
       <c r="B54" t="n">
         <v>99118</v>
@@ -6895,7 +6885,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -6909,13 +6899,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>525682</v>
+        <v>525680</v>
       </c>
       <c r="R54" t="n">
-        <v>6716183</v>
+        <v>6716172</v>
       </c>
       <c r="S54" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6944,7 +6934,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>19:23</t>
+          <t>19:07</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6954,7 +6944,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>19:23</t>
+          <t>19:07</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>1 stjälke</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6981,7 +6976,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129338511</v>
+        <v>127351427</v>
       </c>
       <c r="B55" t="n">
         <v>99118</v>
@@ -7011,12 +7006,12 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -7025,13 +7020,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>525680</v>
+        <v>525690</v>
       </c>
       <c r="R55" t="n">
-        <v>6716143</v>
+        <v>6716183</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7055,27 +7050,27 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-08-09</t>
         </is>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-08-09</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Ca 20 bladrosetter 1 överblommade</t>
+          <t>1 stjälke</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7102,7 +7097,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129338590</v>
+        <v>127351465</v>
       </c>
       <c r="B56" t="n">
         <v>99118</v>
@@ -7132,12 +7127,12 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -7146,10 +7141,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>525673</v>
+        <v>525676</v>
       </c>
       <c r="R56" t="n">
-        <v>6716152</v>
+        <v>6716177</v>
       </c>
       <c r="S56" t="n">
         <v>1</v>
@@ -7176,22 +7171,27 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-08-09</t>
         </is>
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>19:13</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-08-09</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>19:13</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>2 stjälkar</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7218,7 +7218,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129338657</v>
+        <v>127351678</v>
       </c>
       <c r="B57" t="n">
         <v>99118</v>
@@ -7248,17 +7248,12 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -7267,13 +7262,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>525677</v>
+        <v>525682</v>
       </c>
       <c r="R57" t="n">
-        <v>6716163</v>
+        <v>6716183</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7297,27 +7292,22 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-08-09</t>
         </is>
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>19:23</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-08-09</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>10:38</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>1 överblommad</t>
+          <t>19:23</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7344,7 +7334,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129338834</v>
+        <v>129338511</v>
       </c>
       <c r="B58" t="n">
         <v>99118</v>
@@ -7374,7 +7364,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -7388,10 +7378,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>525715</v>
+        <v>525680</v>
       </c>
       <c r="R58" t="n">
-        <v>6716181</v>
+        <v>6716143</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7423,7 +7413,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7433,7 +7423,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:31</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Ca 20 bladrosetter 1 överblommade</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7460,7 +7455,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129338899</v>
+        <v>129338590</v>
       </c>
       <c r="B59" t="n">
         <v>99118</v>
@@ -7490,17 +7485,12 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>dm²</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -7509,13 +7499,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>525712</v>
+        <v>525673</v>
       </c>
       <c r="R59" t="n">
-        <v>6716201</v>
+        <v>6716152</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7544,7 +7534,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7554,7 +7544,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7581,7 +7571,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129339191</v>
+        <v>129338657</v>
       </c>
       <c r="B60" t="n">
         <v>99118</v>
@@ -7611,7 +7601,12 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -7625,10 +7620,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>525746</v>
+        <v>525677</v>
       </c>
       <c r="R60" t="n">
-        <v>6716215</v>
+        <v>6716163</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7660,7 +7655,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7670,7 +7665,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:38</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>1 överblommad</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7697,7 +7697,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129339235</v>
+        <v>129338834</v>
       </c>
       <c r="B61" t="n">
         <v>99118</v>
@@ -7727,7 +7727,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -7741,10 +7741,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>525757</v>
+        <v>525715</v>
       </c>
       <c r="R61" t="n">
-        <v>6716182</v>
+        <v>6716181</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7776,7 +7776,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7786,7 +7786,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7813,7 +7813,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129339499</v>
+        <v>129338899</v>
       </c>
       <c r="B62" t="n">
         <v>99118</v>
@@ -7843,12 +7843,12 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -7862,10 +7862,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>525771</v>
+        <v>525712</v>
       </c>
       <c r="R62" t="n">
-        <v>6716245</v>
+        <v>6716201</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7897,7 +7897,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7907,12 +7907,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>11:09</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Spridda över ca 0,5 m2</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7939,7 +7934,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129339551</v>
+        <v>129339191</v>
       </c>
       <c r="B63" t="n">
         <v>99118</v>
@@ -7969,12 +7964,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -7988,10 +7978,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>525769</v>
+        <v>525746</v>
       </c>
       <c r="R63" t="n">
-        <v>6716224</v>
+        <v>6716215</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8023,7 +8013,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8033,7 +8023,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8060,7 +8050,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129340627</v>
+        <v>129339235</v>
       </c>
       <c r="B64" t="n">
         <v>99118</v>
@@ -8090,12 +8080,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -8109,10 +8094,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>525709</v>
+        <v>525757</v>
       </c>
       <c r="R64" t="n">
-        <v>6716198</v>
+        <v>6716182</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8144,7 +8129,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8154,7 +8139,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8181,7 +8166,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129340696</v>
+        <v>129339499</v>
       </c>
       <c r="B65" t="n">
         <v>99118</v>
@@ -8211,7 +8196,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -8219,16 +8204,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Hundviken, Hundviken, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>525672</v>
+        <v>525771</v>
       </c>
       <c r="R65" t="n">
-        <v>6716190</v>
+        <v>6716245</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8260,7 +8250,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8270,12 +8260,12 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>På stenblock! 2 överblommade</t>
+          <t>Spridda över ca 0,5 m2</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8302,7 +8292,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>130016660</v>
+        <v>129339551</v>
       </c>
       <c r="B66" t="n">
         <v>99118</v>
@@ -8340,19 +8330,24 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Hundviken, Dlr</t>
+          <t>Hundviken, Hundviken, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>525602</v>
+        <v>525769</v>
       </c>
       <c r="R66" t="n">
-        <v>6716070</v>
+        <v>6716224</v>
       </c>
       <c r="S66" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8376,22 +8371,22 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2025-12-07</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2025-12-07</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8418,10 +8413,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>131821961</v>
+        <v>129340627</v>
       </c>
       <c r="B67" t="n">
-        <v>99195</v>
+        <v>99118</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8448,7 +8443,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -8467,13 +8462,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>525563</v>
+        <v>525709</v>
       </c>
       <c r="R67" t="n">
-        <v>6716039</v>
+        <v>6716198</v>
       </c>
       <c r="S67" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8497,22 +8492,22 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8539,10 +8534,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>131822536</v>
+        <v>129340696</v>
       </c>
       <c r="B68" t="n">
-        <v>99195</v>
+        <v>99118</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8569,7 +8564,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -8577,24 +8572,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Hundviken, Hundviken, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>525573</v>
+        <v>525672</v>
       </c>
       <c r="R68" t="n">
-        <v>6716073</v>
+        <v>6716190</v>
       </c>
       <c r="S68" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8618,22 +8608,27 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>11:59</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>På stenblock! 2 överblommade</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8660,10 +8655,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>131823068</v>
+        <v>130016660</v>
       </c>
       <c r="B69" t="n">
-        <v>99195</v>
+        <v>99118</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8698,21 +8693,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Hundviken, Hundviken, Dlr</t>
+          <t>Hundviken, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>525554</v>
+        <v>525602</v>
       </c>
       <c r="R69" t="n">
-        <v>6716042</v>
+        <v>6716070</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -8739,22 +8729,22 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2025-12-07</t>
         </is>
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2025-12-07</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8781,7 +8771,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>131985054</v>
+        <v>131821961</v>
       </c>
       <c r="B70" t="n">
         <v>99195</v>
@@ -8811,7 +8801,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -8830,10 +8820,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>525629</v>
+        <v>525563</v>
       </c>
       <c r="R70" t="n">
-        <v>6716057</v>
+        <v>6716039</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8860,22 +8850,22 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8902,7 +8892,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>131985295</v>
+        <v>131822536</v>
       </c>
       <c r="B71" t="n">
         <v>99195</v>
@@ -8951,13 +8941,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>525591</v>
+        <v>525573</v>
       </c>
       <c r="R71" t="n">
-        <v>6716100</v>
+        <v>6716073</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8981,22 +8971,22 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9023,7 +9013,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>131985410</v>
+        <v>131823068</v>
       </c>
       <c r="B72" t="n">
         <v>99195</v>
@@ -9053,7 +9043,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -9072,10 +9062,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>525611</v>
+        <v>525554</v>
       </c>
       <c r="R72" t="n">
-        <v>6716076</v>
+        <v>6716042</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -9102,12 +9092,22 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9134,52 +9134,62 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>130044041</v>
+        <v>131985054</v>
       </c>
       <c r="B73" t="n">
-        <v>97989</v>
+        <v>99195</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Hundviken, Dlr</t>
+          <t>Hundviken, Hundviken, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>525776</v>
+        <v>525629</v>
       </c>
       <c r="R73" t="n">
-        <v>6716252</v>
+        <v>6716057</v>
       </c>
       <c r="S73" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -9203,12 +9213,22 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9217,22 +9237,355 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
+          <t>Milada Alexandersson</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Milada Alexandersson</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>131985295</v>
+      </c>
+      <c r="B74" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Hundviken, Hundviken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>525591</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6716100</v>
+      </c>
+      <c r="S74" t="n">
+        <v>10</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Aspeboda</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Milada Alexandersson</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Milada Alexandersson</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>131985410</v>
+      </c>
+      <c r="B75" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Hundviken, Hundviken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>525611</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6716076</v>
+      </c>
+      <c r="S75" t="n">
+        <v>5</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Aspeboda</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Milada Alexandersson</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Milada Alexandersson</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>130044041</v>
+      </c>
+      <c r="B76" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Hundviken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>525776</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6716252</v>
+      </c>
+      <c r="S76" t="n">
+        <v>25</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Aspeboda</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF76" t="inlineStr"/>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
           <t>Daniel Alexandersson</t>
         </is>
       </c>
-      <c r="AX73" t="inlineStr">
+      <c r="AX76" t="inlineStr">
         <is>
           <t>Daniel Alexandersson</t>
         </is>
       </c>
-      <c r="AY73" t="inlineStr"/>
+      <c r="AY76" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
